--- a/subsystems database (normalised).xlsx
+++ b/subsystems database (normalised).xlsx
@@ -8,30 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BD1C1E-94A1-4EDD-917B-7A4033F9269A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC638C42-CC2D-4C7D-92C0-D7C271CAFE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1archive" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId1"/>
+    <sheet name="Feuil1archive" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Feuil1archive!$N$2:$N$35</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Feuil1archive!$O$2:$O$35</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Feuil1archive!$O$58</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Feuil1archive!$B$2:$B$35</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Feuil1archive!$K$2:$K$35</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Feuil1archive!$K$2:$K$35</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Feuil1archive!$L$2:$L$35</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Feuil1archive!$M$2:$M$35</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Feuil1archive!$N$2:$N$35</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Feuil1archive!$L$2:$L$35</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Feuil1archive!$M$2:$M$35</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Feuil1archive!$K$2:$K$35</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Feuil1archive!$Z$2:$Z$35</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Feuil1archive!$O$58</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Feuil1archive!$B$2:$B$35</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Feuil1archive!$B$2:$B$35</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Feuil1archive!$N$2:$N$35</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Feuil1archive!$K$2:$K$35</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Feuil1archive!$L$2:$L$35</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Feuil1archive!$M$2:$M$35</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Feuil1archive!$O$2:$O$35</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Feuil1archive!$Z$2:$Z$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -113,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
   <si>
     <t>md</t>
   </si>
@@ -205,9 +197,6 @@
     <t>heat rejection</t>
   </si>
   <si>
-    <t>0503-CE&amp;R-6</t>
-  </si>
-  <si>
     <t>0507-ESAS-A</t>
   </si>
   <si>
@@ -218,15 +207,6 @@
   </si>
   <si>
     <t>descent stage also performs LOI</t>
-  </si>
-  <si>
-    <t>0507-ESAS-C</t>
-  </si>
-  <si>
-    <t>0507-ESAS-E</t>
-  </si>
-  <si>
-    <t>0507-ESAS-G</t>
   </si>
   <si>
     <t>0605-LLPS-LaRC-1A</t>
@@ -262,9 +242,6 @@
     <t>0605-LLPS-LaRC-2</t>
   </si>
   <si>
-    <t>0605-LLPS-LaRC-3</t>
-  </si>
-  <si>
     <t>0605-LLPS-GFSC-1</t>
   </si>
   <si>
@@ -295,13 +272,7 @@
     <t>0605-LLPS-MSFC-6</t>
   </si>
   <si>
-    <t>0609-LLPS-GSFC</t>
-  </si>
-  <si>
     <t>0609-LLPS-JSC-sortie</t>
-  </si>
-  <si>
-    <t>0609-LLPS-GRC-phase</t>
   </si>
   <si>
     <t>delta</t>
@@ -6736,7 +6707,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.9</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -6774,6 +6745,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{00000001-A623-4CA9-874E-DADECEAF5388}">
           <cx:tx>
             <cx:txData>
+              <cx:f/>
               <cx:v>total masses</cx:v>
             </cx:txData>
           </cx:tx>
@@ -6805,7 +6777,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.12</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -6875,7 +6847,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.14</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -6945,7 +6917,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -7015,7 +6987,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -7085,7 +7057,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -7155,7 +7127,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -17041,8 +17013,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11979233" y="9890166"/>
-              <a:ext cx="5437910" cy="3044042"/>
+              <a:off x="11979728" y="10146871"/>
+              <a:ext cx="5430092" cy="3124794"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17061,7 +17033,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:rPr lang="en-150" sz="1100"/>
                 <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
 La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
               </a:r>
@@ -17119,8 +17091,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11924805" y="13201403"/>
-              <a:ext cx="5437910" cy="3044042"/>
+              <a:off x="11925300" y="13548360"/>
+              <a:ext cx="5430092" cy="3124795"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17139,7 +17111,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:rPr lang="en-150" sz="1100"/>
                 <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
 La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
               </a:r>
@@ -17197,8 +17169,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11924805" y="16556182"/>
-              <a:ext cx="5437910" cy="3044042"/>
+              <a:off x="11925300" y="16988642"/>
+              <a:ext cx="5430092" cy="3124794"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17217,7 +17189,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:rPr lang="en-150" sz="1100"/>
                 <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
 La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
               </a:r>
@@ -17275,8 +17247,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11924805" y="19792208"/>
-              <a:ext cx="5437910" cy="3044042"/>
+              <a:off x="11925300" y="20314920"/>
+              <a:ext cx="5430092" cy="3124794"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17295,7 +17267,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:rPr lang="en-150" sz="1100"/>
                 <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
 La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
               </a:r>
@@ -17353,8 +17325,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11924805" y="23176675"/>
-              <a:ext cx="5437910" cy="3044042"/>
+              <a:off x="11925300" y="23789640"/>
+              <a:ext cx="5430092" cy="3124794"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17373,7 +17345,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:rPr lang="en-150" sz="1100"/>
                 <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
 La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
               </a:r>
@@ -17431,8 +17403,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11924805" y="26383013"/>
-              <a:ext cx="5437910" cy="3044042"/>
+              <a:off x="11925300" y="27081480"/>
+              <a:ext cx="5430092" cy="3124794"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17451,7 +17423,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:rPr lang="en-150" sz="1100"/>
                 <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
 La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
               </a:r>
@@ -17509,8 +17481,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="17844655" y="13355782"/>
-              <a:ext cx="5455722" cy="3077689"/>
+              <a:off x="17846040" y="13548360"/>
+              <a:ext cx="5475119" cy="3124795"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17529,7 +17501,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="fr-FR" sz="1100"/>
+                <a:rPr lang="en-150" sz="1100"/>
                 <a:t>Ce graphique n’est pas disponible dans votre version d’Excel.
 La modification de cette forme ou l’enregistrement de ce classeur dans un autre format de fichier endommagera le graphique de façon irréparable.</a:t>
               </a:r>
@@ -17859,6 +17831,2080 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FB372F-B6E8-4845-B0EA-74D8461302A1}">
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1">
+        <f>((Feuil1archive!B2-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.12676821396752669</v>
+      </c>
+      <c r="C2" s="1">
+        <f>((Feuil1archive!C2-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>8.089250476491941E-2</v>
+      </c>
+      <c r="D2" s="1">
+        <f>((Feuil1archive!D2-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.11473235342707806</v>
+      </c>
+      <c r="E2" s="1">
+        <f>((Feuil1archive!E2-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.12657160229880546</v>
+      </c>
+      <c r="F2" s="1">
+        <f>((Feuil1archive!G2-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.11874851390980423</v>
+      </c>
+      <c r="G2" s="1">
+        <f>((Feuil1archive!H2-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.20338389433389339</v>
+      </c>
+      <c r="H2" s="1">
+        <f>((Feuil1archive!J2-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <f>((Feuil1archive!K2-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>1.4720314033366045E-3</v>
+      </c>
+      <c r="J2" s="1">
+        <f>((Feuil1archive!L2-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>5.14152443549242E-2</v>
+      </c>
+      <c r="K2" s="1">
+        <f>((Feuil1archive!M2-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.16718847839699438</v>
+      </c>
+      <c r="L2" s="1">
+        <f>((Feuil1archive!N2-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <f>((Feuil1archive!O2-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.19990079365079366</v>
+      </c>
+      <c r="N2" s="1">
+        <f>((Feuil1archive!P2-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.13921859545004944</v>
+      </c>
+      <c r="O2" s="1">
+        <f>((Feuil1archive!Q2-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1">
+        <f>((Feuil1archive!B3-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <f>((Feuil1archive!C3-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <f>((Feuil1archive!D3-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <f>((Feuil1archive!E3-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <f>((Feuil1archive!G3-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <f>((Feuil1archive!H3-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>3.447766982306958E-2</v>
+      </c>
+      <c r="H3" s="1">
+        <f>((Feuil1archive!J3-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.1476510067114094</v>
+      </c>
+      <c r="I3" s="1">
+        <f>((Feuil1archive!K3-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>8.6849852796859698E-3</v>
+      </c>
+      <c r="J3" s="1">
+        <f>((Feuil1archive!L3-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <f>((Feuil1archive!M3-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <f>((Feuil1archive!N3-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>8.8189738625363015E-2</v>
+      </c>
+      <c r="M3" s="1">
+        <f>((Feuil1archive!O3-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>5.5803571428571432E-2</v>
+      </c>
+      <c r="N3" s="1">
+        <f>((Feuil1archive!P3-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <f>((Feuil1archive!Q3-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1">
+        <f>((Feuil1archive!B4-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.62542500772741327</v>
+      </c>
+      <c r="C4" s="1">
+        <f>((Feuil1archive!C4-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.58264020312363196</v>
+      </c>
+      <c r="D4" s="1">
+        <f>((Feuil1archive!D4-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.58655266617024893</v>
+      </c>
+      <c r="E4" s="1">
+        <f>((Feuil1archive!E4-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.53663476060647664</v>
+      </c>
+      <c r="F4" s="1">
+        <f>((Feuil1archive!G4-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.65683205199334227</v>
+      </c>
+      <c r="G4" s="1">
+        <f>((Feuil1archive!H4-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.12487818434998936</v>
+      </c>
+      <c r="H4" s="1">
+        <f>((Feuil1archive!J4-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I4" s="1">
+        <f>((Feuil1archive!K4-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.20117762512266929</v>
+      </c>
+      <c r="J4" s="1">
+        <f>((Feuil1archive!L4-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.84925262376762434</v>
+      </c>
+      <c r="K4" s="1">
+        <f>((Feuil1archive!M4-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.2451123634592639</v>
+      </c>
+      <c r="L4" s="1">
+        <f>((Feuil1archive!N4-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.87608906098741535</v>
+      </c>
+      <c r="M4" s="1">
+        <f>((Feuil1archive!O4-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <f>((Feuil1archive!P4-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>9.866468842729971E-2</v>
+      </c>
+      <c r="O4" s="1">
+        <f>((Feuil1archive!Q4-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1">
+        <f>((Feuil1archive!B5-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.73023373152239135</v>
+      </c>
+      <c r="C5" s="1">
+        <f>((Feuil1archive!C5-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.45306133444683161</v>
+      </c>
+      <c r="D5" s="1">
+        <f>((Feuil1archive!D5-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.58655266617024893</v>
+      </c>
+      <c r="E5" s="1">
+        <f>((Feuil1archive!E5-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.80993664554851619</v>
+      </c>
+      <c r="F5" s="1">
+        <f>((Feuil1archive!G5-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.61870888483791708</v>
+      </c>
+      <c r="G5" s="1">
+        <f>((Feuil1archive!H5-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.12487818434998936</v>
+      </c>
+      <c r="H5" s="1">
+        <f>((Feuil1archive!J5-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.1476510067114094</v>
+      </c>
+      <c r="I5" s="1">
+        <f>((Feuil1archive!K5-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.24599280340202814</v>
+      </c>
+      <c r="J5" s="1">
+        <f>((Feuil1archive!L5-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.57044418530690133</v>
+      </c>
+      <c r="K5" s="1">
+        <f>((Feuil1archive!M5-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.2451123634592639</v>
+      </c>
+      <c r="L5" s="1">
+        <f>((Feuil1archive!N5-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <f>((Feuil1archive!O5-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.49851190476190477</v>
+      </c>
+      <c r="N5" s="1">
+        <f>((Feuil1archive!P5-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>9.866468842729971E-2</v>
+      </c>
+      <c r="O5" s="1">
+        <f>((Feuil1archive!Q5-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1">
+        <f>((Feuil1archive!B6-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <f>((Feuil1archive!C6-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.79606818380802935</v>
+      </c>
+      <c r="D6" s="1">
+        <f>((Feuil1archive!D6-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.84738746202045212</v>
+      </c>
+      <c r="E6" s="1">
+        <f>((Feuil1archive!E6-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <f>((Feuil1archive!G6-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="G6" s="1">
+        <f>((Feuil1archive!H6-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.60067036607061974</v>
+      </c>
+      <c r="H6" s="1">
+        <f>((Feuil1archive!J6-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I6" s="1">
+        <f>((Feuil1archive!K6-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.21573438011122015</v>
+      </c>
+      <c r="J6" s="1">
+        <f>((Feuil1archive!L6-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <f>((Feuil1archive!M6-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.18040770889862939</v>
+      </c>
+      <c r="L6" s="1">
+        <f>((Feuil1archive!N6-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.26911907066795743</v>
+      </c>
+      <c r="M6" s="1">
+        <f>((Feuil1archive!O6-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.2078373015873016</v>
+      </c>
+      <c r="N6" s="1">
+        <f>((Feuil1archive!P6-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.79302670623145399</v>
+      </c>
+      <c r="O6" s="1">
+        <f>((Feuil1archive!Q6-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.95621181262729127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <f>((Feuil1archive!B7-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.45208094692630779</v>
+      </c>
+      <c r="C7" s="1">
+        <f>((Feuil1archive!C7-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.31560266970184742</v>
+      </c>
+      <c r="D7" s="1">
+        <f>((Feuil1archive!D7-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.38210358210884954</v>
+      </c>
+      <c r="E7" s="1">
+        <f>((Feuil1archive!E7-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.46921032501029758</v>
+      </c>
+      <c r="F7" s="1">
+        <f>((Feuil1archive!G7-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.40907109455496554</v>
+      </c>
+      <c r="G7" s="1">
+        <f>((Feuil1archive!H7-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.20100493342529022</v>
+      </c>
+      <c r="H7" s="1">
+        <f>((Feuil1archive!J7-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.4563758389261745</v>
+      </c>
+      <c r="I7" s="1">
+        <f>((Feuil1archive!K7-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.38779849525678772</v>
+      </c>
+      <c r="J7" s="1">
+        <f>((Feuil1archive!L7-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.31729036361708896</v>
+      </c>
+      <c r="K7" s="1">
+        <f>((Feuil1archive!M7-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>5.4477144646211645E-2</v>
+      </c>
+      <c r="L7" s="1">
+        <f>((Feuil1archive!N7-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.76282671829622462</v>
+      </c>
+      <c r="M7" s="1">
+        <f>((Feuil1archive!O7-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <f>((Feuil1archive!P7-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>5.1681503461918889E-2</v>
+      </c>
+      <c r="O7" s="1">
+        <f>((Feuil1archive!Q7-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
+        <f>((Feuil1archive!B8-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.63519791268932169</v>
+      </c>
+      <c r="C8" s="1">
+        <f>((Feuil1archive!C8-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.69612273624234755</v>
+      </c>
+      <c r="D8" s="1">
+        <f>((Feuil1archive!D8-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.561197053098341</v>
+      </c>
+      <c r="E8" s="1">
+        <f>((Feuil1archive!E8-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.54237196712629698</v>
+      </c>
+      <c r="F8" s="1">
+        <f>((Feuil1archive!G8-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.66923595149401605</v>
+      </c>
+      <c r="G8" s="1">
+        <f>((Feuil1archive!H8-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>2.9719748005863276E-2</v>
+      </c>
+      <c r="H8" s="1">
+        <f>((Feuil1archive!J8-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34228187919463088</v>
+      </c>
+      <c r="I8" s="1">
+        <f>((Feuil1archive!K8-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.25580634609093883</v>
+      </c>
+      <c r="J8" s="1">
+        <f>((Feuil1archive!L8-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.46061698293225911</v>
+      </c>
+      <c r="K8" s="1">
+        <f>((Feuil1archive!M8-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.29729353649203372</v>
+      </c>
+      <c r="L8" s="1">
+        <f>((Feuil1archive!N8-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.54695062923523718</v>
+      </c>
+      <c r="M8" s="1">
+        <f>((Feuil1archive!O8-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.53125</v>
+      </c>
+      <c r="N8" s="1">
+        <f>((Feuil1archive!P8-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.81231454005934722</v>
+      </c>
+      <c r="O8" s="1">
+        <f>((Feuil1archive!Q8-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.76782077393075354</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <f>((Feuil1archive!B9-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.59035618829433267</v>
+      </c>
+      <c r="C9" s="1">
+        <f>((Feuil1archive!C9-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.68440406516658703</v>
+      </c>
+      <c r="D9" s="1">
+        <f>((Feuil1archive!D9-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.51046188397712011</v>
+      </c>
+      <c r="E9" s="1">
+        <f>((Feuil1archive!E9-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.50184375183884822</v>
+      </c>
+      <c r="F9" s="1">
+        <f>((Feuil1archive!G9-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.62380122057541409</v>
+      </c>
+      <c r="G9" s="1">
+        <f>((Feuil1archive!H9-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>2.9719748005863276E-2</v>
+      </c>
+      <c r="H9" s="1">
+        <f>((Feuil1archive!J9-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.26845637583892618</v>
+      </c>
+      <c r="I9" s="1">
+        <f>((Feuil1archive!K9-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.2508995747464835</v>
+      </c>
+      <c r="J9" s="1">
+        <f>((Feuil1archive!L9-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.44407929608820101</v>
+      </c>
+      <c r="K9" s="1">
+        <f>((Feuil1archive!M9-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.29729353649203372</v>
+      </c>
+      <c r="L9" s="1">
+        <f>((Feuil1archive!N9-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.54695062923523718</v>
+      </c>
+      <c r="M9" s="1">
+        <f>((Feuil1archive!O9-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.52827380952380953</v>
+      </c>
+      <c r="N9" s="1">
+        <f>((Feuil1archive!P9-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.80365974282888231</v>
+      </c>
+      <c r="O9" s="1">
+        <f>((Feuil1archive!Q9-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.75509164969450104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <f>((Feuil1archive!B10-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.46328569610356557</v>
+      </c>
+      <c r="C10" s="1">
+        <f>((Feuil1archive!C10-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.53845946619432794</v>
+      </c>
+      <c r="D10" s="1">
+        <f>((Feuil1archive!D10-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.40669301990379714</v>
+      </c>
+      <c r="E10" s="1">
+        <f>((Feuil1archive!E10-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.38707510346586116</v>
+      </c>
+      <c r="F10" s="1">
+        <f>((Feuil1archive!G10-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.49498692240627723</v>
+      </c>
+      <c r="G10" s="1">
+        <f>((Feuil1archive!H10-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>2.9719748005863276E-2</v>
+      </c>
+      <c r="H10" s="1">
+        <f>((Feuil1archive!J10-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34899328859060402</v>
+      </c>
+      <c r="I10" s="1">
+        <f>((Feuil1archive!K10-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.23323519790644423</v>
+      </c>
+      <c r="J10" s="1">
+        <f>((Feuil1archive!L10-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.18498886886462418</v>
+      </c>
+      <c r="K10" s="1">
+        <f>((Feuil1archive!M10-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.29729353649203372</v>
+      </c>
+      <c r="L10" s="1">
+        <f>((Feuil1archive!N10-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.54695062923523718</v>
+      </c>
+      <c r="M10" s="1">
+        <f>((Feuil1archive!O10-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.51984126984126988</v>
+      </c>
+      <c r="N10" s="1">
+        <f>((Feuil1archive!P10-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.67235410484668645</v>
+      </c>
+      <c r="O10" s="1">
+        <f>((Feuil1archive!Q10-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.60794297352342164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
+        <f>((Feuil1archive!B11-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.4405125547737232</v>
+      </c>
+      <c r="C11" s="1">
+        <f>((Feuil1archive!C11-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.53239808460341731</v>
+      </c>
+      <c r="D11" s="1">
+        <f>((Feuil1archive!D11-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.38097826217081399</v>
+      </c>
+      <c r="E11" s="1">
+        <f>((Feuil1archive!E11-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.36648000313830098</v>
+      </c>
+      <c r="F11" s="1">
+        <f>((Feuil1archive!G11-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.47192280256796387</v>
+      </c>
+      <c r="G11" s="1">
+        <f>((Feuil1archive!H11-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>2.9719748005863276E-2</v>
+      </c>
+      <c r="H11" s="1">
+        <f>((Feuil1archive!J11-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34899328859060402</v>
+      </c>
+      <c r="I11" s="1">
+        <f>((Feuil1archive!K11-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.23045469414458619</v>
+      </c>
+      <c r="J11" s="1">
+        <f>((Feuil1archive!L11-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.178628220078448</v>
+      </c>
+      <c r="K11" s="1">
+        <f>((Feuil1archive!M11-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.29729353649203372</v>
+      </c>
+      <c r="L11" s="1">
+        <f>((Feuil1archive!N11-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.54695062923523718</v>
+      </c>
+      <c r="M11" s="1">
+        <f>((Feuil1archive!O11-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.51835317460317465</v>
+      </c>
+      <c r="N11" s="1">
+        <f>((Feuil1archive!P11-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.66543026706231456</v>
+      </c>
+      <c r="O11" s="1">
+        <f>((Feuil1archive!Q11-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.60183299389002032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1">
+        <f>((Feuil1archive!B12-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.55184412443862618</v>
+      </c>
+      <c r="C12" s="1">
+        <f>((Feuil1archive!C12-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.51205878193169496</v>
+      </c>
+      <c r="D12" s="1">
+        <f>((Feuil1archive!D12-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.48747662566830835</v>
+      </c>
+      <c r="E12" s="1">
+        <f>((Feuil1archive!E12-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.50503108879430403</v>
+      </c>
+      <c r="F12" s="1">
+        <f>((Feuil1archive!G12-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.55407386858999763</v>
+      </c>
+      <c r="G12" s="1">
+        <f>((Feuil1archive!H12-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.37024600329288859</v>
+      </c>
+      <c r="H12" s="1">
+        <f>((Feuil1archive!J12-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I12" s="1">
+        <f>((Feuil1archive!K12-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>1.3738959764474975E-2</v>
+      </c>
+      <c r="J12" s="1">
+        <f>((Feuil1archive!L12-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.5838015477578713</v>
+      </c>
+      <c r="K12" s="1">
+        <f>((Feuil1archive!M12-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.54498017115424757</v>
+      </c>
+      <c r="L12" s="1">
+        <f>((Feuil1archive!N12-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.67957405614714428</v>
+      </c>
+      <c r="M12" s="1">
+        <f>((Feuil1archive!O12-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.41220238095238093</v>
+      </c>
+      <c r="N12" s="1">
+        <f>((Feuil1archive!P12-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.33877349159248271</v>
+      </c>
+      <c r="O12" s="1">
+        <f>((Feuil1archive!Q12-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.68024439918533608</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1">
+        <f>((Feuil1archive!B13-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.56317387588865253</v>
+      </c>
+      <c r="C13" s="1">
+        <f>((Feuil1archive!C13-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.37177147244428582</v>
+      </c>
+      <c r="D13" s="1">
+        <f>((Feuil1archive!D13-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.42673329199179239</v>
+      </c>
+      <c r="E13" s="1">
+        <f>((Feuil1archive!E13-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.64274856324657237</v>
+      </c>
+      <c r="F13" s="1">
+        <f>((Feuil1archive!G13-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.46253071253071254</v>
+      </c>
+      <c r="G13" s="1">
+        <f>((Feuil1archive!H13-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.44435121518455278</v>
+      </c>
+      <c r="H13" s="1">
+        <f>((Feuil1archive!J13-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34228187919463088</v>
+      </c>
+      <c r="I13" s="1">
+        <f>((Feuil1archive!K13-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.54072620215897937</v>
+      </c>
+      <c r="J13" s="1">
+        <f>((Feuil1archive!L13-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.20491890172797625</v>
+      </c>
+      <c r="K13" s="1">
+        <f>((Feuil1archive!M13-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.19084394350518336</v>
+      </c>
+      <c r="L13" s="1">
+        <f>((Feuil1archive!N13-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.16456921587608905</v>
+      </c>
+      <c r="M13" s="1">
+        <f>((Feuil1archive!O13-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <f>((Feuil1archive!P13-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.26211671612265086</v>
+      </c>
+      <c r="O13" s="1">
+        <f>((Feuil1archive!Q13-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1">
+        <f>((Feuil1archive!B14-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.46391070746740853</v>
+      </c>
+      <c r="C14" s="1">
+        <f>((Feuil1archive!C14-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.43662825546702949</v>
+      </c>
+      <c r="D14" s="1">
+        <f>((Feuil1archive!D14-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.3016791210054135</v>
+      </c>
+      <c r="E14" s="1">
+        <f>((Feuil1archive!E14-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.53303061804915364</v>
+      </c>
+      <c r="F14" s="1">
+        <f>((Feuil1archive!G14-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.37812078941111199</v>
+      </c>
+      <c r="G14" s="1">
+        <f>((Feuil1archive!H14-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.79080151613538274</v>
+      </c>
+      <c r="H14" s="1">
+        <f>((Feuil1archive!J14-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I14" s="1">
+        <f>((Feuil1archive!K14-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.10827608766764803</v>
+      </c>
+      <c r="J14" s="1">
+        <f>((Feuil1archive!L14-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.44725962048128909</v>
+      </c>
+      <c r="K14" s="1">
+        <f>((Feuil1archive!M14-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.23815487372156127</v>
+      </c>
+      <c r="L14" s="1">
+        <f>((Feuil1archive!N14-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M14" s="1">
+        <f>((Feuil1archive!O14-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.18253968253968253</v>
+      </c>
+      <c r="N14" s="1">
+        <f>((Feuil1archive!P14-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.54277942631058362</v>
+      </c>
+      <c r="O14" s="1">
+        <f>((Feuil1archive!Q14-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.52087576374745415</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1">
+        <f>((Feuil1archive!B15-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.87356588301605487</v>
+      </c>
+      <c r="C15" s="1">
+        <f>((Feuil1archive!C15-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.58607498602514796</v>
+      </c>
+      <c r="D15" s="1">
+        <f>((Feuil1archive!D15-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <f>((Feuil1archive!E15-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.6473824608202734</v>
+      </c>
+      <c r="F15" s="1">
+        <f>((Feuil1archive!G15-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <f>((Feuil1archive!H15-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>7.4379610384912351E-2</v>
+      </c>
+      <c r="H15" s="1">
+        <f>((Feuil1archive!J15-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I15" s="1">
+        <f>((Feuil1archive!K15-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.32401046777886816</v>
+      </c>
+      <c r="J15" s="1">
+        <f>((Feuil1archive!L15-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.33361602883494118</v>
+      </c>
+      <c r="K15" s="1">
+        <f>((Feuil1archive!M15-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.14631600918388646</v>
+      </c>
+      <c r="L15" s="1">
+        <f>((Feuil1archive!N15-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.11229428848015489</v>
+      </c>
+      <c r="M15" s="1">
+        <f>((Feuil1archive!O15-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.57886904761904767</v>
+      </c>
+      <c r="N15" s="1">
+        <f>((Feuil1archive!P15-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.58679525222551931</v>
+      </c>
+      <c r="O15" s="1">
+        <f>((Feuil1archive!Q15-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.78309572301425667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1">
+        <f>((Feuil1archive!B16-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.42296678121420395</v>
+      </c>
+      <c r="C16" s="1">
+        <f>((Feuil1archive!C16-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.28960607754527518</v>
+      </c>
+      <c r="D16" s="1">
+        <f>((Feuil1archive!D16-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.21172535489478256</v>
+      </c>
+      <c r="E16" s="1">
+        <f>((Feuil1archive!E16-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.59032912931761572</v>
+      </c>
+      <c r="F16" s="1">
+        <f>((Feuil1archive!G16-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.26042244590631686</v>
+      </c>
+      <c r="G16" s="1">
+        <f>((Feuil1archive!H16-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.70575282269671014</v>
+      </c>
+      <c r="H16" s="1">
+        <f>((Feuil1archive!J16-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>8.0536912751677847E-2</v>
+      </c>
+      <c r="I16" s="1">
+        <f>((Feuil1archive!K16-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>9.1593065096499837E-2</v>
+      </c>
+      <c r="J16" s="1">
+        <f>((Feuil1archive!L16-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.28909148733170781</v>
+      </c>
+      <c r="K16" s="1">
+        <f>((Feuil1archive!M16-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L16" s="1">
+        <f>((Feuil1archive!N16-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M16" s="1">
+        <f>((Feuil1archive!O16-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.14136904761904762</v>
+      </c>
+      <c r="N16" s="1">
+        <f>((Feuil1archive!P16-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.33160237388724034</v>
+      </c>
+      <c r="O16" s="1">
+        <f>((Feuil1archive!Q16-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.40071283095723015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1">
+        <f>((Feuil1archive!B17-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.41809169257622869</v>
+      </c>
+      <c r="C17" s="1">
+        <f>((Feuil1archive!C17-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.43858136731298958</v>
+      </c>
+      <c r="D17" s="1">
+        <f>((Feuil1archive!D17-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.21309010460686825</v>
+      </c>
+      <c r="E17" s="1">
+        <f>((Feuil1archive!E17-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.52417962850361888</v>
+      </c>
+      <c r="F17" s="1">
+        <f>((Feuil1archive!G17-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.30538162796227314</v>
+      </c>
+      <c r="G17" s="1">
+        <f>((Feuil1archive!H17-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.64272267510271341</v>
+      </c>
+      <c r="H17" s="1">
+        <f>((Feuil1archive!J17-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34899328859060402</v>
+      </c>
+      <c r="I17" s="1">
+        <f>((Feuil1archive!K17-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.14785737651292116</v>
+      </c>
+      <c r="J17" s="1">
+        <f>((Feuil1archive!L17-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.37326407293543939</v>
+      </c>
+      <c r="K17" s="1">
+        <f>((Feuil1archive!M17-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L17" s="1">
+        <f>((Feuil1archive!N17-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M17" s="1">
+        <f>((Feuil1archive!O17-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.13095238095238096</v>
+      </c>
+      <c r="N17" s="1">
+        <f>((Feuil1archive!P17-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.66345202769535117</v>
+      </c>
+      <c r="O17" s="1">
+        <f>((Feuil1archive!Q17-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.47708757637474541</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1">
+        <f>((Feuil1archive!B18-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.20287187039764362</v>
+      </c>
+      <c r="C18" s="1">
+        <f>((Feuil1archive!C18-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.13025909038866926</v>
+      </c>
+      <c r="D18" s="1">
+        <f>((Feuil1archive!D18-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.21129438130149236</v>
+      </c>
+      <c r="E18" s="1">
+        <f>((Feuil1archive!E18-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.17391581507561343</v>
+      </c>
+      <c r="F18" s="1">
+        <f>((Feuil1archive!G18-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.21318459221685029</v>
+      </c>
+      <c r="G18" s="1">
+        <f>((Feuil1archive!H18-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>4.5943677917876027E-2</v>
+      </c>
+      <c r="H18" s="1">
+        <f>((Feuil1archive!J18-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>8.0536912751677847E-2</v>
+      </c>
+      <c r="I18" s="1">
+        <f>((Feuil1archive!K18-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <f>((Feuil1archive!L18-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>9.0003180324393084E-2</v>
+      </c>
+      <c r="K18" s="1">
+        <f>((Feuil1archive!M18-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L18" s="1">
+        <f>((Feuil1archive!N18-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M18" s="1">
+        <f>((Feuil1archive!O18-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.10367063492063493</v>
+      </c>
+      <c r="N18" s="1">
+        <f>((Feuil1archive!P18-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.21686449060336302</v>
+      </c>
+      <c r="O18" s="1">
+        <f>((Feuil1archive!Q18-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.23421588594704684</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1">
+        <f>((Feuil1archive!B19-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.20569010345642652</v>
+      </c>
+      <c r="C19" s="1">
+        <f>((Feuil1archive!C19-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.22629831426243088</v>
+      </c>
+      <c r="D19" s="1">
+        <f>((Feuil1archive!D19-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.2096183728831415</v>
+      </c>
+      <c r="E19" s="1">
+        <f>((Feuil1archive!E19-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.14674989702449834</v>
+      </c>
+      <c r="F19" s="1">
+        <f>((Feuil1archive!G19-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.24005310295632876</v>
+      </c>
+      <c r="G19" s="1">
+        <f>((Feuil1archive!H19-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>2.7714699620058156E-3</v>
+      </c>
+      <c r="H19" s="1">
+        <f>((Feuil1archive!J19-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34899328859060402</v>
+      </c>
+      <c r="I19" s="1">
+        <f>((Feuil1archive!K19-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>4.350670592083742E-2</v>
+      </c>
+      <c r="J19" s="1">
+        <f>((Feuil1archive!L19-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.14894519240962578</v>
+      </c>
+      <c r="K19" s="1">
+        <f>((Feuil1archive!M19-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L19" s="1">
+        <f>((Feuil1archive!N19-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M19" s="1">
+        <f>((Feuil1archive!O19-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.10813492063492064</v>
+      </c>
+      <c r="N19" s="1">
+        <f>((Feuil1archive!P19-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.40454995054401582</v>
+      </c>
+      <c r="O19" s="1">
+        <f>((Feuil1archive!Q19-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.29226069246435843</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="1">
+        <f>((Feuil1archive!B20-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.2059741995309006</v>
+      </c>
+      <c r="C20" s="1">
+        <f>((Feuil1archive!C20-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.13025909038866926</v>
+      </c>
+      <c r="D20" s="1">
+        <f>((Feuil1archive!D20-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.21783081413306069</v>
+      </c>
+      <c r="E20" s="1">
+        <f>((Feuil1archive!E20-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.17391581507561343</v>
+      </c>
+      <c r="F20" s="1">
+        <f>((Feuil1archive!G20-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.21859396052944441</v>
+      </c>
+      <c r="G20" s="1">
+        <f>((Feuil1archive!H20-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>3.1071766101429501E-2</v>
+      </c>
+      <c r="H20" s="1">
+        <f>((Feuil1archive!J20-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>8.0536912751677847E-2</v>
+      </c>
+      <c r="I20" s="1">
+        <f>((Feuil1archive!K20-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <f>((Feuil1archive!L20-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>9.0003180324393084E-2</v>
+      </c>
+      <c r="K20" s="1">
+        <f>((Feuil1archive!M20-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L20" s="1">
+        <f>((Feuil1archive!N20-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M20" s="1">
+        <f>((Feuil1archive!O20-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.10367063492063493</v>
+      </c>
+      <c r="N20" s="1">
+        <f>((Feuil1archive!P20-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.21686449060336302</v>
+      </c>
+      <c r="O20" s="1">
+        <f>((Feuil1archive!Q20-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.23421588594704684</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="1">
+        <f>((Feuil1archive!B21-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.20632647866324846</v>
+      </c>
+      <c r="C21" s="1">
+        <f>((Feuil1archive!C21-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.22629831426243088</v>
+      </c>
+      <c r="D21" s="1">
+        <f>((Feuil1archive!D21-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.21095917961782218</v>
+      </c>
+      <c r="E21" s="1">
+        <f>((Feuil1archive!E21-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.14674989702449834</v>
+      </c>
+      <c r="F21" s="1">
+        <f>((Feuil1archive!G21-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.24116271696916858</v>
+      </c>
+      <c r="G21" s="1">
+        <f>((Feuil1archive!H21-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <f>((Feuil1archive!J21-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34899328859060402</v>
+      </c>
+      <c r="I21" s="1">
+        <f>((Feuil1archive!K21-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>4.350670592083742E-2</v>
+      </c>
+      <c r="J21" s="1">
+        <f>((Feuil1archive!L21-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.14894519240962578</v>
+      </c>
+      <c r="K21" s="1">
+        <f>((Feuil1archive!M21-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L21" s="1">
+        <f>((Feuil1archive!N21-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M21" s="1">
+        <f>((Feuil1archive!O21-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.10813492063492064</v>
+      </c>
+      <c r="N21" s="1">
+        <f>((Feuil1archive!P21-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.40454995054401582</v>
+      </c>
+      <c r="O21" s="1">
+        <f>((Feuil1archive!Q21-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.29226069246435843</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1">
+        <f>((Feuil1archive!B22-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.2059741995309006</v>
+      </c>
+      <c r="C22" s="1">
+        <f>((Feuil1archive!C22-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.13025909038866926</v>
+      </c>
+      <c r="D22" s="1">
+        <f>((Feuil1archive!D22-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.21783081413306069</v>
+      </c>
+      <c r="E22" s="1">
+        <f>((Feuil1archive!E22-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.17391581507561343</v>
+      </c>
+      <c r="F22" s="1">
+        <f>((Feuil1archive!G22-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.21859396052944441</v>
+      </c>
+      <c r="G22" s="1">
+        <f>((Feuil1archive!H22-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>3.1071766101429501E-2</v>
+      </c>
+      <c r="H22" s="1">
+        <f>((Feuil1archive!J22-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>8.0536912751677847E-2</v>
+      </c>
+      <c r="I22" s="1">
+        <f>((Feuil1archive!K22-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <f>((Feuil1archive!L22-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>9.0003180324393084E-2</v>
+      </c>
+      <c r="K22" s="1">
+        <f>((Feuil1archive!M22-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L22" s="1">
+        <f>((Feuil1archive!N22-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M22" s="1">
+        <f>((Feuil1archive!O22-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.10367063492063493</v>
+      </c>
+      <c r="N22" s="1">
+        <f>((Feuil1archive!P22-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.21686449060336302</v>
+      </c>
+      <c r="O22" s="1">
+        <f>((Feuil1archive!Q22-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.23421588594704684</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1">
+        <f>((Feuil1archive!B23-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.48272923144057167</v>
+      </c>
+      <c r="C23" s="1">
+        <f>((Feuil1archive!C23-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.29095305123214421</v>
+      </c>
+      <c r="D23" s="1">
+        <f>((Feuil1archive!D23-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.33397819752477498</v>
+      </c>
+      <c r="E23" s="1">
+        <f>((Feuil1archive!E23-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.59359002020281271</v>
+      </c>
+      <c r="F23" s="1">
+        <f>((Feuil1archive!G23-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.36199175715304749</v>
+      </c>
+      <c r="G23" s="1">
+        <f>((Feuil1archive!H23-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.59676622354422082</v>
+      </c>
+      <c r="H23" s="1">
+        <f>((Feuil1archive!J23-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.34899328859060402</v>
+      </c>
+      <c r="I23" s="1">
+        <f>((Feuil1archive!K23-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>9.2574419365390903E-2</v>
+      </c>
+      <c r="J23" s="1">
+        <f>((Feuil1archive!L23-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.29078766034135484</v>
+      </c>
+      <c r="K23" s="1">
+        <f>((Feuil1archive!M23-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.12544353997077856</v>
+      </c>
+      <c r="L23" s="1">
+        <f>((Feuil1archive!N23-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M23" s="1">
+        <f>((Feuil1archive!O23-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.14136904761904762</v>
+      </c>
+      <c r="N23" s="1">
+        <f>((Feuil1archive!P23-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.33234421364985162</v>
+      </c>
+      <c r="O23" s="1">
+        <f>((Feuil1archive!Q23-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.40224032586558045</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1">
+        <f>((Feuil1archive!B25-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.16524618629429627</v>
+      </c>
+      <c r="C24" s="1">
+        <f>((Feuil1archive!C25-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.36759585401499184</v>
+      </c>
+      <c r="D24" s="1">
+        <f>((Feuil1archive!D25-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.1328332443452673</v>
+      </c>
+      <c r="E24" s="1">
+        <f>((Feuil1archive!E25-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>8.6680854402447868E-2</v>
+      </c>
+      <c r="F24" s="1">
+        <f>((Feuil1archive!G25-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.21807878259491162</v>
+      </c>
+      <c r="G24" s="1">
+        <f>((Feuil1archive!H25-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>5.8574915804237092E-2</v>
+      </c>
+      <c r="H24" s="1">
+        <f>((Feuil1archive!J25-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <f>((Feuil1archive!K25-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.11432777232580962</v>
+      </c>
+      <c r="J24" s="1">
+        <f>((Feuil1archive!L25-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.10548075903742182</v>
+      </c>
+      <c r="K24" s="1">
+        <f>((Feuil1archive!M25-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.35086620747234398</v>
+      </c>
+      <c r="L24" s="1">
+        <f>((Feuil1archive!N25-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>4.9370764762826716E-2</v>
+      </c>
+      <c r="M24" s="1">
+        <f>((Feuil1archive!O25-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.39632936507936506</v>
+      </c>
+      <c r="N24" s="1">
+        <f>((Feuil1archive!P25-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.57467853610286845</v>
+      </c>
+      <c r="O24" s="1">
+        <f>((Feuil1archive!Q25-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.42769857433808556</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1">
+        <f>((Feuil1archive!B26-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.45411507481954222</v>
+      </c>
+      <c r="C25" s="1">
+        <f>((Feuil1archive!C26-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.62466578215394564</v>
+      </c>
+      <c r="D25" s="1">
+        <f>((Feuil1archive!D26-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.2237447295520987</v>
+      </c>
+      <c r="E25" s="1">
+        <f>((Feuil1archive!E26-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.52324794539356256</v>
+      </c>
+      <c r="F25" s="1">
+        <f>((Feuil1archive!G26-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.36894665926923992</v>
+      </c>
+      <c r="G25" s="1">
+        <f>((Feuil1archive!H26-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.56416299492883204</v>
+      </c>
+      <c r="H25" s="1">
+        <f>((Feuil1archive!J26-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.51006711409395977</v>
+      </c>
+      <c r="I25" s="1">
+        <f>((Feuil1archive!K26-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.24223094537127904</v>
+      </c>
+      <c r="J25" s="1">
+        <f>((Feuil1archive!L26-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.42118096045796671</v>
+      </c>
+      <c r="K25" s="1">
+        <f>((Feuil1archive!M26-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.23815487372156127</v>
+      </c>
+      <c r="L25" s="1">
+        <f>((Feuil1archive!N26-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.26815101645692158</v>
+      </c>
+      <c r="M25" s="1">
+        <f>((Feuil1archive!O26-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.5982142857142857</v>
+      </c>
+      <c r="N25" s="1">
+        <f>((Feuil1archive!P26-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.70771513353115723</v>
+      </c>
+      <c r="O25" s="1">
+        <f>((Feuil1archive!Q26-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.70112016293279023</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1">
+        <f>((Feuil1archive!B27-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.45412643866252117</v>
+      </c>
+      <c r="C26" s="1">
+        <f>((Feuil1archive!C27-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.63598036112364542</v>
+      </c>
+      <c r="D26" s="1">
+        <f>((Feuil1archive!D27-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.21974625232546166</v>
+      </c>
+      <c r="E26" s="1">
+        <f>((Feuil1archive!E27-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.52324794539356256</v>
+      </c>
+      <c r="F26" s="1">
+        <f>((Feuil1archive!G27-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.36896647380518349</v>
+      </c>
+      <c r="G26" s="1">
+        <f>((Feuil1archive!H27-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.56411412924105453</v>
+      </c>
+      <c r="H26" s="1">
+        <f>((Feuil1archive!J27-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.51006711409395977</v>
+      </c>
+      <c r="I26" s="1">
+        <f>((Feuil1archive!K27-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.28655544651619236</v>
+      </c>
+      <c r="J26" s="1">
+        <f>((Feuil1archive!L27-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.42118096045796671</v>
+      </c>
+      <c r="K26" s="1">
+        <f>((Feuil1archive!M27-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.23815487372156127</v>
+      </c>
+      <c r="L26" s="1">
+        <f>((Feuil1archive!N27-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.26815101645692158</v>
+      </c>
+      <c r="M26" s="1">
+        <f>((Feuil1archive!O27-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.59077380952380953</v>
+      </c>
+      <c r="N26" s="1">
+        <f>((Feuil1archive!P27-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.6708704253214639</v>
+      </c>
+      <c r="O26" s="1">
+        <f>((Feuil1archive!Q27-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.73217922606924646</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1">
+        <f>((Feuil1archive!B28-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.45410371097656327</v>
+      </c>
+      <c r="C27" s="1">
+        <f>((Feuil1archive!C28-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.61725742687616603</v>
+      </c>
+      <c r="D27" s="1">
+        <f>((Feuil1archive!D28-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.22635451408924503</v>
+      </c>
+      <c r="E27" s="1">
+        <f>((Feuil1archive!E28-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.52324794539356256</v>
+      </c>
+      <c r="F27" s="1">
+        <f>((Feuil1archive!G28-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.36892684473329634</v>
+      </c>
+      <c r="G27" s="1">
+        <f>((Feuil1archive!H28-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.56421186411052715</v>
+      </c>
+      <c r="H27" s="1">
+        <f>((Feuil1archive!J28-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.51006711409395977</v>
+      </c>
+      <c r="I27" s="1">
+        <f>((Feuil1archive!K28-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.30062152437029765</v>
+      </c>
+      <c r="J27" s="1">
+        <f>((Feuil1archive!L28-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.42118096045796671</v>
+      </c>
+      <c r="K27" s="1">
+        <f>((Feuil1archive!M28-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.23815487372156127</v>
+      </c>
+      <c r="L27" s="1">
+        <f>((Feuil1archive!N28-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.31461761858664083</v>
+      </c>
+      <c r="M27" s="1">
+        <f>((Feuil1archive!O28-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.59077380952380953</v>
+      </c>
+      <c r="N27" s="1">
+        <f>((Feuil1archive!P28-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.58382789317507422</v>
+      </c>
+      <c r="O27" s="1">
+        <f>((Feuil1archive!Q28-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.70162932790224031</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="1">
+        <f>((Feuil1archive!B29-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.55233276968672163</v>
+      </c>
+      <c r="C28" s="1">
+        <f>((Feuil1archive!C29-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.47818239370693894</v>
+      </c>
+      <c r="D28" s="1">
+        <f>((Feuil1archive!D29-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.44289480174017559</v>
+      </c>
+      <c r="E28" s="1">
+        <f>((Feuil1archive!E29-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.56407037639997648</v>
+      </c>
+      <c r="F28" s="1">
+        <f>((Feuil1archive!G29-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.50721249108345878</v>
+      </c>
+      <c r="G28" s="1">
+        <f>((Feuil1archive!H29-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.546604717525907</v>
+      </c>
+      <c r="H28" s="1">
+        <f>((Feuil1archive!J29-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I28" s="1">
+        <f>((Feuil1archive!K29-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.10827608766764803</v>
+      </c>
+      <c r="J28" s="1">
+        <f>((Feuil1archive!L29-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.44725962048128909</v>
+      </c>
+      <c r="K28" s="1">
+        <f>((Feuil1archive!M29-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.23815487372156127</v>
+      </c>
+      <c r="L28" s="1">
+        <f>((Feuil1archive!N29-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>3.8722168441432718E-2</v>
+      </c>
+      <c r="M28" s="1">
+        <f>((Feuil1archive!O29-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.18253968253968253</v>
+      </c>
+      <c r="N28" s="1">
+        <f>((Feuil1archive!P29-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.54277942631058362</v>
+      </c>
+      <c r="O28" s="1">
+        <f>((Feuil1archive!Q29-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.83503054989816705</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="1">
+        <f>((Feuil1archive!B30-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.51061610211094755</v>
+      </c>
+      <c r="C29" s="1">
+        <f>((Feuil1archive!C30-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.95359675648736197</v>
+      </c>
+      <c r="D29" s="1">
+        <f>((Feuil1archive!D30-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.14595399596321398</v>
+      </c>
+      <c r="E29" s="1">
+        <f>((Feuil1archive!E30-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.6050644332424534</v>
+      </c>
+      <c r="F29" s="1">
+        <f>((Feuil1archive!G30-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.40134342553697394</v>
+      </c>
+      <c r="G29" s="1">
+        <f>((Feuil1archive!H30-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.85570243058607431</v>
+      </c>
+      <c r="H29" s="1">
+        <f>((Feuil1archive!J30-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I29" s="1">
+        <f>((Feuil1archive!K30-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.66961072947333988</v>
+      </c>
+      <c r="J29" s="1">
+        <f>((Feuil1archive!L30-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.60606381850948798</v>
+      </c>
+      <c r="K29" s="1">
+        <f>((Feuil1archive!M30-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.56237389549850414</v>
+      </c>
+      <c r="L29" s="1">
+        <f>((Feuil1archive!N30-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.39883833494675702</v>
+      </c>
+      <c r="M29" s="1">
+        <f>((Feuil1archive!O30-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.16617063492063491</v>
+      </c>
+      <c r="N29" s="1">
+        <f>((Feuil1archive!P30-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="O29" s="1">
+        <f>((Feuil1archive!Q30-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.94908350305498979</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="1">
+        <f>((Feuil1archive!B31-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.51061610211094755</v>
+      </c>
+      <c r="C30" s="1">
+        <f>((Feuil1archive!C31-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.93931883540655037</v>
+      </c>
+      <c r="D30" s="1">
+        <f>((Feuil1archive!D31-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.1510299071730766</v>
+      </c>
+      <c r="E30" s="1">
+        <f>((Feuil1archive!E31-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.6050644332424534</v>
+      </c>
+      <c r="F30" s="1">
+        <f>((Feuil1archive!G31-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.40134342553697394</v>
+      </c>
+      <c r="G30" s="1">
+        <f>((Feuil1archive!H31-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.85570243058607431</v>
+      </c>
+      <c r="H30" s="1">
+        <f>((Feuil1archive!J31-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I30" s="1">
+        <f>((Feuil1archive!K31-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.65080143931959433</v>
+      </c>
+      <c r="J30" s="1">
+        <f>((Feuil1archive!L31-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.62111735397010492</v>
+      </c>
+      <c r="K30" s="1">
+        <f>((Feuil1archive!M31-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.56237389549850414</v>
+      </c>
+      <c r="L30" s="1">
+        <f>((Feuil1archive!N31-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.39883833494675702</v>
+      </c>
+      <c r="M30" s="1">
+        <f>((Feuil1archive!O31-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.16617063492063491</v>
+      </c>
+      <c r="N30" s="1">
+        <f>((Feuil1archive!P31-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="O30" s="1">
+        <f>((Feuil1archive!Q31-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.86354378818737276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="1">
+        <f>((Feuil1archive!B32-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.51099110892925326</v>
+      </c>
+      <c r="C31" s="1">
+        <f>((Feuil1archive!C32-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="D31" s="1">
+        <f>((Feuil1archive!D32-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.13024740278552599</v>
+      </c>
+      <c r="E31" s="1">
+        <f>((Feuil1archive!E32-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.6050644332424534</v>
+      </c>
+      <c r="F31" s="1">
+        <f>((Feuil1archive!G32-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.40199730522311167</v>
+      </c>
+      <c r="G31" s="1">
+        <f>((Feuil1archive!H32-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.85393060167969459</v>
+      </c>
+      <c r="H31" s="1">
+        <f>((Feuil1archive!J32-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I31" s="1">
+        <f>((Feuil1archive!K32-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <f>((Feuil1archive!L32-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.55899501749178415</v>
+      </c>
+      <c r="K31" s="1">
+        <f>((Feuil1archive!M32-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.56237389549850414</v>
+      </c>
+      <c r="L31" s="1">
+        <f>((Feuil1archive!N32-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.39883833494675702</v>
+      </c>
+      <c r="M31" s="1">
+        <f>((Feuil1archive!O32-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.16617063492063491</v>
+      </c>
+      <c r="N31" s="1">
+        <f>((Feuil1archive!P32-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.70103857566765582</v>
+      </c>
+      <c r="O31" s="1">
+        <f>((Feuil1archive!Q32-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="1">
+        <f>((Feuil1archive!B33-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.51060473826796859</v>
+      </c>
+      <c r="C32" s="1">
+        <f>((Feuil1archive!C33-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.6632565782827432</v>
+      </c>
+      <c r="D32" s="1">
+        <f>((Feuil1archive!D33-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.24914822857881666</v>
+      </c>
+      <c r="E32" s="1">
+        <f>((Feuil1archive!E33-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.6050644332424534</v>
+      </c>
+      <c r="F32" s="1">
+        <f>((Feuil1archive!G33-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.40132361100103037</v>
+      </c>
+      <c r="G32" s="1">
+        <f>((Feuil1archive!H33-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.85575618225876859</v>
+      </c>
+      <c r="H32" s="1">
+        <f>((Feuil1archive!J33-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I32" s="1">
+        <f>((Feuil1archive!K33-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.22980045796532547</v>
+      </c>
+      <c r="J32" s="1">
+        <f>((Feuil1archive!L33-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.49305629174175764</v>
+      </c>
+      <c r="K32" s="1">
+        <f>((Feuil1archive!M33-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.56237389549850414</v>
+      </c>
+      <c r="L32" s="1">
+        <f>((Feuil1archive!N33-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.39883833494675702</v>
+      </c>
+      <c r="M32" s="1">
+        <f>((Feuil1archive!O33-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.16617063492063491</v>
+      </c>
+      <c r="N32" s="1">
+        <f>((Feuil1archive!P33-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.87512363996043518</v>
+      </c>
+      <c r="O32" s="1">
+        <f>((Feuil1archive!Q33-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.65173116089613037</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1">
+        <f>((Feuil1archive!B34-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.51061610211094755</v>
+      </c>
+      <c r="C33" s="1">
+        <f>((Feuil1archive!C34-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.62325145978273311</v>
+      </c>
+      <c r="D33" s="1">
+        <f>((Feuil1archive!D34-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.26339430013479892</v>
+      </c>
+      <c r="E33" s="1">
+        <f>((Feuil1archive!E34-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.6050644332424534</v>
+      </c>
+      <c r="F33" s="1">
+        <f>((Feuil1archive!G34-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.40134342553697394</v>
+      </c>
+      <c r="G33" s="1">
+        <f>((Feuil1archive!H34-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>0.85570243058607431</v>
+      </c>
+      <c r="H33" s="1">
+        <f>((Feuil1archive!J34-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I33" s="1">
+        <f>((Feuil1archive!K34-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.19414458619561661</v>
+      </c>
+      <c r="J33" s="1">
+        <f>((Feuil1archive!L34-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.49793278914449274</v>
+      </c>
+      <c r="K33" s="1">
+        <f>((Feuil1archive!M34-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>0.56237389549850414</v>
+      </c>
+      <c r="L33" s="1">
+        <f>((Feuil1archive!N34-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.39883833494675702</v>
+      </c>
+      <c r="M33" s="1">
+        <f>((Feuil1archive!O34-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.16617063492063491</v>
+      </c>
+      <c r="N33" s="1">
+        <f>((Feuil1archive!P34-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.79698318496538079</v>
+      </c>
+      <c r="O33" s="1">
+        <f>((Feuil1archive!Q34-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0.60947046843177188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1">
+        <f>((Feuil1archive!B35-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
+        <v>0.44676266841215301</v>
+      </c>
+      <c r="C34" s="1">
+        <f>((Feuil1archive!C35-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
+        <v>0.69464106518679158</v>
+      </c>
+      <c r="D34" s="1">
+        <f>((Feuil1archive!D35-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
+        <v>0.14803703499745005</v>
+      </c>
+      <c r="E34" s="1">
+        <f>((Feuil1archive!E35-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
+        <v>0.55943647882627545</v>
+      </c>
+      <c r="F34" s="1">
+        <f>((Feuil1archive!G35-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
+        <v>0.32688039946104464</v>
+      </c>
+      <c r="G34" s="1">
+        <f>((Feuil1archive!H35-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="1">
+        <f>((Feuil1archive!J35-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
+        <v>0.93288590604026844</v>
+      </c>
+      <c r="I34" s="1">
+        <f>((Feuil1archive!K35-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
+        <v>0.73405299313052008</v>
+      </c>
+      <c r="J34" s="1">
+        <f>((Feuil1archive!L35-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
+        <v>0.44513940421923037</v>
+      </c>
+      <c r="K34" s="1">
+        <f>((Feuil1archive!M35-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <f>((Feuil1archive!N35-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
+        <v>0.22652468538238141</v>
+      </c>
+      <c r="M34" s="1">
+        <f>((Feuil1archive!O35-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
+        <v>0.51537698412698407</v>
+      </c>
+      <c r="N34" s="1">
+        <f>((Feuil1archive!P35-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
+        <v>0.31478733926805141</v>
+      </c>
+      <c r="O34" s="1">
+        <f>((Feuil1archive!Q35-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
   <dimension ref="A1:Z57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -17897,16 +19943,16 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>4</v>
@@ -17933,7 +19979,7 @@
         <v>11</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -18670,7 +20716,7 @@
     </row>
     <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1">
         <v>53600</v>
@@ -18820,7 +20866,7 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1">
         <f>35054+10808</f>
@@ -18887,7 +20933,7 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Z14">
         <f t="shared" si="5"/>
@@ -18896,7 +20942,7 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1">
         <f>10790+39791+31330</f>
@@ -18969,7 +21015,7 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1">
         <f>34504+7755</f>
@@ -19037,7 +21083,7 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Z16">
         <f t="shared" si="5"/>
@@ -19046,7 +21092,7 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1">
         <f>34018+7812</f>
@@ -19114,7 +21160,7 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
@@ -19123,7 +21169,7 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1">
         <f>15154+7737</f>
@@ -19197,7 +21243,7 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B19" s="1">
         <f>15472+7667</f>
@@ -19270,7 +21316,7 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B20" s="1">
         <f>13564+9600</f>
@@ -19342,7 +21388,7 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1">
         <f>13882+9313</f>
@@ -19414,7 +21460,7 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B22" s="1">
         <f>13564+9600</f>
@@ -19487,7 +21533,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1">
         <f>33067+14451</f>
@@ -19551,7 +21597,7 @@
       </c>
       <c r="S23" s="1"/>
       <c r="V23" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Z23">
         <f t="shared" si="5"/>
@@ -19560,7 +21606,7 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1">
         <f>33067+14234</f>
@@ -19626,7 +21672,7 @@
       </c>
       <c r="S24" s="1"/>
       <c r="V24" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Z24">
         <f t="shared" si="5"/>
@@ -19635,7 +21681,7 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B25" s="1">
         <f>14030+5550</f>
@@ -19708,7 +21754,7 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1">
         <f>39807+5193</f>
@@ -19780,7 +21826,7 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B27" s="1">
         <f>40007+4994</f>
@@ -19851,7 +21897,7 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B28" s="1">
         <f>39779+5220</f>
@@ -19917,7 +21963,7 @@
       </c>
       <c r="S28" s="1"/>
       <c r="V28" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Z28">
         <f t="shared" si="5"/>
@@ -19926,7 +21972,7 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B29" s="1">
         <f>53643</f>
@@ -19996,7 +22042,7 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B30" s="1">
         <f>45001+4971</f>
@@ -20068,7 +22114,7 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B31" s="1">
         <f>45001+4971</f>
@@ -20140,7 +22186,7 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B32" s="1">
         <f>45000+5005</f>
@@ -20213,7 +22259,7 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B33" s="1">
         <f>45000+4971</f>
@@ -20285,7 +22331,7 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B34" s="1">
         <f>45001+4971</f>
@@ -20356,7 +22402,7 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B35" s="1">
         <f>37668+6685</f>
@@ -20419,7 +22465,7 @@
       </c>
       <c r="S35" s="1"/>
       <c r="V35" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Z35">
         <f t="shared" si="5"/>
@@ -20530,2505 +22576,4 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FB372F-B6E8-4845-B0EA-74D8461302A1}">
-  <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1">
-        <f>((Feuil1archive!B2-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.12676821396752669</v>
-      </c>
-      <c r="C2" s="1">
-        <f>((Feuil1archive!C2-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>8.089250476491941E-2</v>
-      </c>
-      <c r="D2" s="1">
-        <f>((Feuil1archive!D2-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.11473235342707806</v>
-      </c>
-      <c r="E2" s="1">
-        <f>((Feuil1archive!E2-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.12657160229880546</v>
-      </c>
-      <c r="F2" s="1">
-        <f>((Feuil1archive!G2-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.11874851390980423</v>
-      </c>
-      <c r="G2" s="1">
-        <f>((Feuil1archive!H2-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.20338389433389339</v>
-      </c>
-      <c r="H2" s="1">
-        <f>((Feuil1archive!J2-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="1">
-        <f>((Feuil1archive!K2-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>1.4720314033366045E-3</v>
-      </c>
-      <c r="J2" s="1">
-        <f>((Feuil1archive!L2-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>5.14152443549242E-2</v>
-      </c>
-      <c r="K2" s="1">
-        <f>((Feuil1archive!M2-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.16718847839699438</v>
-      </c>
-      <c r="L2" s="1">
-        <f>((Feuil1archive!N2-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="1">
-        <f>((Feuil1archive!O2-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.19990079365079366</v>
-      </c>
-      <c r="N2" s="1">
-        <f>((Feuil1archive!P2-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.13921859545004944</v>
-      </c>
-      <c r="O2" s="1">
-        <f>((Feuil1archive!Q2-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1">
-        <f>((Feuil1archive!B3-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="1">
-        <f>((Feuil1archive!C3-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
-        <f>((Feuil1archive!D3-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
-        <f>((Feuil1archive!E3-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <f>((Feuil1archive!G3-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <f>((Feuil1archive!H3-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>3.447766982306958E-2</v>
-      </c>
-      <c r="H3" s="1">
-        <f>((Feuil1archive!J3-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.1476510067114094</v>
-      </c>
-      <c r="I3" s="1">
-        <f>((Feuil1archive!K3-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>8.6849852796859698E-3</v>
-      </c>
-      <c r="J3" s="1">
-        <f>((Feuil1archive!L3-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <f>((Feuil1archive!M3-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="1">
-        <f>((Feuil1archive!N3-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>8.8189738625363015E-2</v>
-      </c>
-      <c r="M3" s="1">
-        <f>((Feuil1archive!O3-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>5.5803571428571432E-2</v>
-      </c>
-      <c r="N3" s="1">
-        <f>((Feuil1archive!P3-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="1">
-        <f>((Feuil1archive!Q3-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1">
-        <f>((Feuil1archive!B4-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.62542500772741327</v>
-      </c>
-      <c r="C4" s="1">
-        <f>((Feuil1archive!C4-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.58264020312363196</v>
-      </c>
-      <c r="D4" s="1">
-        <f>((Feuil1archive!D4-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.58655266617024893</v>
-      </c>
-      <c r="E4" s="1">
-        <f>((Feuil1archive!E4-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.53663476060647664</v>
-      </c>
-      <c r="F4" s="1">
-        <f>((Feuil1archive!G4-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.65683205199334227</v>
-      </c>
-      <c r="G4" s="1">
-        <f>((Feuil1archive!H4-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.12487818434998936</v>
-      </c>
-      <c r="H4" s="1">
-        <f>((Feuil1archive!J4-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I4" s="1">
-        <f>((Feuil1archive!K4-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.20117762512266929</v>
-      </c>
-      <c r="J4" s="1">
-        <f>((Feuil1archive!L4-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.84925262376762434</v>
-      </c>
-      <c r="K4" s="1">
-        <f>((Feuil1archive!M4-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.2451123634592639</v>
-      </c>
-      <c r="L4" s="1">
-        <f>((Feuil1archive!N4-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.87608906098741535</v>
-      </c>
-      <c r="M4" s="1">
-        <f>((Feuil1archive!O4-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <f>((Feuil1archive!P4-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>9.866468842729971E-2</v>
-      </c>
-      <c r="O4" s="1">
-        <f>((Feuil1archive!Q4-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1">
-        <f>((Feuil1archive!B5-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.73023373152239135</v>
-      </c>
-      <c r="C5" s="1">
-        <f>((Feuil1archive!C5-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.45306133444683161</v>
-      </c>
-      <c r="D5" s="1">
-        <f>((Feuil1archive!D5-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.58655266617024893</v>
-      </c>
-      <c r="E5" s="1">
-        <f>((Feuil1archive!E5-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.80993664554851619</v>
-      </c>
-      <c r="F5" s="1">
-        <f>((Feuil1archive!G5-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.61870888483791708</v>
-      </c>
-      <c r="G5" s="1">
-        <f>((Feuil1archive!H5-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.12487818434998936</v>
-      </c>
-      <c r="H5" s="1">
-        <f>((Feuil1archive!J5-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.1476510067114094</v>
-      </c>
-      <c r="I5" s="1">
-        <f>((Feuil1archive!K5-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.24599280340202814</v>
-      </c>
-      <c r="J5" s="1">
-        <f>((Feuil1archive!L5-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.57044418530690133</v>
-      </c>
-      <c r="K5" s="1">
-        <f>((Feuil1archive!M5-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.2451123634592639</v>
-      </c>
-      <c r="L5" s="1">
-        <f>((Feuil1archive!N5-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <f>((Feuil1archive!O5-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.49851190476190477</v>
-      </c>
-      <c r="N5" s="1">
-        <f>((Feuil1archive!P5-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>9.866468842729971E-2</v>
-      </c>
-      <c r="O5" s="1">
-        <f>((Feuil1archive!Q5-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1">
-        <f>((Feuil1archive!B6-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
-        <f>((Feuil1archive!C6-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.79606818380802935</v>
-      </c>
-      <c r="D6" s="1">
-        <f>((Feuil1archive!D6-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.84738746202045212</v>
-      </c>
-      <c r="E6" s="1">
-        <f>((Feuil1archive!E6-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <f>((Feuil1archive!G6-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.93548387096774188</v>
-      </c>
-      <c r="G6" s="1">
-        <f>((Feuil1archive!H6-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.60067036607061974</v>
-      </c>
-      <c r="H6" s="1">
-        <f>((Feuil1archive!J6-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I6" s="1">
-        <f>((Feuil1archive!K6-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.21573438011122015</v>
-      </c>
-      <c r="J6" s="1">
-        <f>((Feuil1archive!L6-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <f>((Feuil1archive!M6-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.18040770889862939</v>
-      </c>
-      <c r="L6" s="1">
-        <f>((Feuil1archive!N6-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.26911907066795743</v>
-      </c>
-      <c r="M6" s="1">
-        <f>((Feuil1archive!O6-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.2078373015873016</v>
-      </c>
-      <c r="N6" s="1">
-        <f>((Feuil1archive!P6-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.79302670623145399</v>
-      </c>
-      <c r="O6" s="1">
-        <f>((Feuil1archive!Q6-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.95621181262729127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1">
-        <f>((Feuil1archive!B7-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.45208094692630779</v>
-      </c>
-      <c r="C7" s="1">
-        <f>((Feuil1archive!C7-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.31560266970184742</v>
-      </c>
-      <c r="D7" s="1">
-        <f>((Feuil1archive!D7-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.38210358210884954</v>
-      </c>
-      <c r="E7" s="1">
-        <f>((Feuil1archive!E7-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.46921032501029758</v>
-      </c>
-      <c r="F7" s="1">
-        <f>((Feuil1archive!G7-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.40907109455496554</v>
-      </c>
-      <c r="G7" s="1">
-        <f>((Feuil1archive!H7-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.20100493342529022</v>
-      </c>
-      <c r="H7" s="1">
-        <f>((Feuil1archive!J7-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.4563758389261745</v>
-      </c>
-      <c r="I7" s="1">
-        <f>((Feuil1archive!K7-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.38779849525678772</v>
-      </c>
-      <c r="J7" s="1">
-        <f>((Feuil1archive!L7-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.31729036361708896</v>
-      </c>
-      <c r="K7" s="1">
-        <f>((Feuil1archive!M7-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>5.4477144646211645E-2</v>
-      </c>
-      <c r="L7" s="1">
-        <f>((Feuil1archive!N7-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.76282671829622462</v>
-      </c>
-      <c r="M7" s="1">
-        <f>((Feuil1archive!O7-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <f>((Feuil1archive!P7-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>5.1681503461918889E-2</v>
-      </c>
-      <c r="O7" s="1">
-        <f>((Feuil1archive!Q7-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1">
-        <f>((Feuil1archive!B8-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.63519791268932169</v>
-      </c>
-      <c r="C8" s="1">
-        <f>((Feuil1archive!C8-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.69612273624234755</v>
-      </c>
-      <c r="D8" s="1">
-        <f>((Feuil1archive!D8-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.561197053098341</v>
-      </c>
-      <c r="E8" s="1">
-        <f>((Feuil1archive!E8-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.54237196712629698</v>
-      </c>
-      <c r="F8" s="1">
-        <f>((Feuil1archive!G8-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.66923595149401605</v>
-      </c>
-      <c r="G8" s="1">
-        <f>((Feuil1archive!H8-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>2.9719748005863276E-2</v>
-      </c>
-      <c r="H8" s="1">
-        <f>((Feuil1archive!J8-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34228187919463088</v>
-      </c>
-      <c r="I8" s="1">
-        <f>((Feuil1archive!K8-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.25580634609093883</v>
-      </c>
-      <c r="J8" s="1">
-        <f>((Feuil1archive!L8-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.46061698293225911</v>
-      </c>
-      <c r="K8" s="1">
-        <f>((Feuil1archive!M8-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.29729353649203372</v>
-      </c>
-      <c r="L8" s="1">
-        <f>((Feuil1archive!N8-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.54695062923523718</v>
-      </c>
-      <c r="M8" s="1">
-        <f>((Feuil1archive!O8-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.53125</v>
-      </c>
-      <c r="N8" s="1">
-        <f>((Feuil1archive!P8-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.81231454005934722</v>
-      </c>
-      <c r="O8" s="1">
-        <f>((Feuil1archive!Q8-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.76782077393075354</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1">
-        <f>((Feuil1archive!B9-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.59035618829433267</v>
-      </c>
-      <c r="C9" s="1">
-        <f>((Feuil1archive!C9-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.68440406516658703</v>
-      </c>
-      <c r="D9" s="1">
-        <f>((Feuil1archive!D9-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.51046188397712011</v>
-      </c>
-      <c r="E9" s="1">
-        <f>((Feuil1archive!E9-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.50184375183884822</v>
-      </c>
-      <c r="F9" s="1">
-        <f>((Feuil1archive!G9-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.62380122057541409</v>
-      </c>
-      <c r="G9" s="1">
-        <f>((Feuil1archive!H9-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>2.9719748005863276E-2</v>
-      </c>
-      <c r="H9" s="1">
-        <f>((Feuil1archive!J9-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.26845637583892618</v>
-      </c>
-      <c r="I9" s="1">
-        <f>((Feuil1archive!K9-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.2508995747464835</v>
-      </c>
-      <c r="J9" s="1">
-        <f>((Feuil1archive!L9-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.44407929608820101</v>
-      </c>
-      <c r="K9" s="1">
-        <f>((Feuil1archive!M9-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.29729353649203372</v>
-      </c>
-      <c r="L9" s="1">
-        <f>((Feuil1archive!N9-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.54695062923523718</v>
-      </c>
-      <c r="M9" s="1">
-        <f>((Feuil1archive!O9-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.52827380952380953</v>
-      </c>
-      <c r="N9" s="1">
-        <f>((Feuil1archive!P9-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.80365974282888231</v>
-      </c>
-      <c r="O9" s="1">
-        <f>((Feuil1archive!Q9-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.75509164969450104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1">
-        <f>((Feuil1archive!B10-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.46328569610356557</v>
-      </c>
-      <c r="C10" s="1">
-        <f>((Feuil1archive!C10-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.53845946619432794</v>
-      </c>
-      <c r="D10" s="1">
-        <f>((Feuil1archive!D10-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.40669301990379714</v>
-      </c>
-      <c r="E10" s="1">
-        <f>((Feuil1archive!E10-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.38707510346586116</v>
-      </c>
-      <c r="F10" s="1">
-        <f>((Feuil1archive!G10-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.49498692240627723</v>
-      </c>
-      <c r="G10" s="1">
-        <f>((Feuil1archive!H10-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>2.9719748005863276E-2</v>
-      </c>
-      <c r="H10" s="1">
-        <f>((Feuil1archive!J10-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34899328859060402</v>
-      </c>
-      <c r="I10" s="1">
-        <f>((Feuil1archive!K10-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.23323519790644423</v>
-      </c>
-      <c r="J10" s="1">
-        <f>((Feuil1archive!L10-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.18498886886462418</v>
-      </c>
-      <c r="K10" s="1">
-        <f>((Feuil1archive!M10-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.29729353649203372</v>
-      </c>
-      <c r="L10" s="1">
-        <f>((Feuil1archive!N10-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.54695062923523718</v>
-      </c>
-      <c r="M10" s="1">
-        <f>((Feuil1archive!O10-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.51984126984126988</v>
-      </c>
-      <c r="N10" s="1">
-        <f>((Feuil1archive!P10-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.67235410484668645</v>
-      </c>
-      <c r="O10" s="1">
-        <f>((Feuil1archive!Q10-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.60794297352342164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1">
-        <f>((Feuil1archive!B11-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.4405125547737232</v>
-      </c>
-      <c r="C11" s="1">
-        <f>((Feuil1archive!C11-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.53239808460341731</v>
-      </c>
-      <c r="D11" s="1">
-        <f>((Feuil1archive!D11-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.38097826217081399</v>
-      </c>
-      <c r="E11" s="1">
-        <f>((Feuil1archive!E11-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.36648000313830098</v>
-      </c>
-      <c r="F11" s="1">
-        <f>((Feuil1archive!G11-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.47192280256796387</v>
-      </c>
-      <c r="G11" s="1">
-        <f>((Feuil1archive!H11-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>2.9719748005863276E-2</v>
-      </c>
-      <c r="H11" s="1">
-        <f>((Feuil1archive!J11-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34899328859060402</v>
-      </c>
-      <c r="I11" s="1">
-        <f>((Feuil1archive!K11-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.23045469414458619</v>
-      </c>
-      <c r="J11" s="1">
-        <f>((Feuil1archive!L11-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.178628220078448</v>
-      </c>
-      <c r="K11" s="1">
-        <f>((Feuil1archive!M11-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.29729353649203372</v>
-      </c>
-      <c r="L11" s="1">
-        <f>((Feuil1archive!N11-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.54695062923523718</v>
-      </c>
-      <c r="M11" s="1">
-        <f>((Feuil1archive!O11-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.51835317460317465</v>
-      </c>
-      <c r="N11" s="1">
-        <f>((Feuil1archive!P11-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.66543026706231456</v>
-      </c>
-      <c r="O11" s="1">
-        <f>((Feuil1archive!Q11-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.60183299389002032</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1">
-        <f>((Feuil1archive!B12-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.55184412443862618</v>
-      </c>
-      <c r="C12" s="1">
-        <f>((Feuil1archive!C12-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.51205878193169496</v>
-      </c>
-      <c r="D12" s="1">
-        <f>((Feuil1archive!D12-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.48747662566830835</v>
-      </c>
-      <c r="E12" s="1">
-        <f>((Feuil1archive!E12-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.50503108879430403</v>
-      </c>
-      <c r="F12" s="1">
-        <f>((Feuil1archive!G12-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.55407386858999763</v>
-      </c>
-      <c r="G12" s="1">
-        <f>((Feuil1archive!H12-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.37024600329288859</v>
-      </c>
-      <c r="H12" s="1">
-        <f>((Feuil1archive!J12-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I12" s="1">
-        <f>((Feuil1archive!K12-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>1.3738959764474975E-2</v>
-      </c>
-      <c r="J12" s="1">
-        <f>((Feuil1archive!L12-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.5838015477578713</v>
-      </c>
-      <c r="K12" s="1">
-        <f>((Feuil1archive!M12-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.54498017115424757</v>
-      </c>
-      <c r="L12" s="1">
-        <f>((Feuil1archive!N12-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.67957405614714428</v>
-      </c>
-      <c r="M12" s="1">
-        <f>((Feuil1archive!O12-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.41220238095238093</v>
-      </c>
-      <c r="N12" s="1">
-        <f>((Feuil1archive!P12-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.33877349159248271</v>
-      </c>
-      <c r="O12" s="1">
-        <f>((Feuil1archive!Q12-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.68024439918533608</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="1">
-        <f>((Feuil1archive!B13-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.56317387588865253</v>
-      </c>
-      <c r="C13" s="1">
-        <f>((Feuil1archive!C13-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.37177147244428582</v>
-      </c>
-      <c r="D13" s="1">
-        <f>((Feuil1archive!D13-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.42673329199179239</v>
-      </c>
-      <c r="E13" s="1">
-        <f>((Feuil1archive!E13-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.64274856324657237</v>
-      </c>
-      <c r="F13" s="1">
-        <f>((Feuil1archive!G13-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.46253071253071254</v>
-      </c>
-      <c r="G13" s="1">
-        <f>((Feuil1archive!H13-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.44435121518455278</v>
-      </c>
-      <c r="H13" s="1">
-        <f>((Feuil1archive!J13-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34228187919463088</v>
-      </c>
-      <c r="I13" s="1">
-        <f>((Feuil1archive!K13-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.54072620215897937</v>
-      </c>
-      <c r="J13" s="1">
-        <f>((Feuil1archive!L13-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.20491890172797625</v>
-      </c>
-      <c r="K13" s="1">
-        <f>((Feuil1archive!M13-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.19084394350518336</v>
-      </c>
-      <c r="L13" s="1">
-        <f>((Feuil1archive!N13-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.16456921587608905</v>
-      </c>
-      <c r="M13" s="1">
-        <f>((Feuil1archive!O13-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <f>((Feuil1archive!P13-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.26211671612265086</v>
-      </c>
-      <c r="O13" s="1">
-        <f>((Feuil1archive!Q13-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O14" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="1">
-        <f>((Feuil1archive!B14-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.46391070746740853</v>
-      </c>
-      <c r="C15" s="1">
-        <f>((Feuil1archive!C14-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.43662825546702949</v>
-      </c>
-      <c r="D15" s="1">
-        <f>((Feuil1archive!D14-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.3016791210054135</v>
-      </c>
-      <c r="E15" s="1">
-        <f>((Feuil1archive!E14-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.53303061804915364</v>
-      </c>
-      <c r="F15" s="1">
-        <f>((Feuil1archive!G14-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.37812078941111199</v>
-      </c>
-      <c r="G15" s="1">
-        <f>((Feuil1archive!H14-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.79080151613538274</v>
-      </c>
-      <c r="H15" s="1">
-        <f>((Feuil1archive!J14-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I15" s="1">
-        <f>((Feuil1archive!K14-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.10827608766764803</v>
-      </c>
-      <c r="J15" s="1">
-        <f>((Feuil1archive!L14-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.44725962048128909</v>
-      </c>
-      <c r="K15" s="1">
-        <f>((Feuil1archive!M14-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.23815487372156127</v>
-      </c>
-      <c r="L15" s="1">
-        <f>((Feuil1archive!N14-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M15" s="1">
-        <f>((Feuil1archive!O14-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.18253968253968253</v>
-      </c>
-      <c r="N15" s="1">
-        <f>((Feuil1archive!P14-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.54277942631058362</v>
-      </c>
-      <c r="O15" s="1">
-        <f>((Feuil1archive!Q14-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.52087576374745415</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="1">
-        <f>((Feuil1archive!B15-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.87356588301605487</v>
-      </c>
-      <c r="C16" s="1">
-        <f>((Feuil1archive!C15-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.58607498602514796</v>
-      </c>
-      <c r="D16" s="1">
-        <f>((Feuil1archive!D15-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <f>((Feuil1archive!E15-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.6473824608202734</v>
-      </c>
-      <c r="F16" s="1">
-        <f>((Feuil1archive!G15-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <f>((Feuil1archive!H15-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>7.4379610384912351E-2</v>
-      </c>
-      <c r="H16" s="1">
-        <f>((Feuil1archive!J15-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I16" s="1">
-        <f>((Feuil1archive!K15-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.32401046777886816</v>
-      </c>
-      <c r="J16" s="1">
-        <f>((Feuil1archive!L15-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.33361602883494118</v>
-      </c>
-      <c r="K16" s="1">
-        <f>((Feuil1archive!M15-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.14631600918388646</v>
-      </c>
-      <c r="L16" s="1">
-        <f>((Feuil1archive!N15-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.11229428848015489</v>
-      </c>
-      <c r="M16" s="1">
-        <f>((Feuil1archive!O15-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.57886904761904767</v>
-      </c>
-      <c r="N16" s="1">
-        <f>((Feuil1archive!P15-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.58679525222551931</v>
-      </c>
-      <c r="O16" s="1">
-        <f>((Feuil1archive!Q15-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.78309572301425667</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O17" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O18" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O19" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="1">
-        <f>((Feuil1archive!B16-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.42296678121420395</v>
-      </c>
-      <c r="C20" s="1">
-        <f>((Feuil1archive!C16-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.28960607754527518</v>
-      </c>
-      <c r="D20" s="1">
-        <f>((Feuil1archive!D16-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.21172535489478256</v>
-      </c>
-      <c r="E20" s="1">
-        <f>((Feuil1archive!E16-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.59032912931761572</v>
-      </c>
-      <c r="F20" s="1">
-        <f>((Feuil1archive!G16-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.26042244590631686</v>
-      </c>
-      <c r="G20" s="1">
-        <f>((Feuil1archive!H16-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.70575282269671014</v>
-      </c>
-      <c r="H20" s="1">
-        <f>((Feuil1archive!J16-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>8.0536912751677847E-2</v>
-      </c>
-      <c r="I20" s="1">
-        <f>((Feuil1archive!K16-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>9.1593065096499837E-2</v>
-      </c>
-      <c r="J20" s="1">
-        <f>((Feuil1archive!L16-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.28909148733170781</v>
-      </c>
-      <c r="K20" s="1">
-        <f>((Feuil1archive!M16-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L20" s="1">
-        <f>((Feuil1archive!N16-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M20" s="1">
-        <f>((Feuil1archive!O16-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.14136904761904762</v>
-      </c>
-      <c r="N20" s="1">
-        <f>((Feuil1archive!P16-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.33160237388724034</v>
-      </c>
-      <c r="O20" s="1">
-        <f>((Feuil1archive!Q16-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.40071283095723015</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="1">
-        <f>((Feuil1archive!B17-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.41809169257622869</v>
-      </c>
-      <c r="C21" s="1">
-        <f>((Feuil1archive!C17-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.43858136731298958</v>
-      </c>
-      <c r="D21" s="1">
-        <f>((Feuil1archive!D17-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.21309010460686825</v>
-      </c>
-      <c r="E21" s="1">
-        <f>((Feuil1archive!E17-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.52417962850361888</v>
-      </c>
-      <c r="F21" s="1">
-        <f>((Feuil1archive!G17-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.30538162796227314</v>
-      </c>
-      <c r="G21" s="1">
-        <f>((Feuil1archive!H17-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.64272267510271341</v>
-      </c>
-      <c r="H21" s="1">
-        <f>((Feuil1archive!J17-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34899328859060402</v>
-      </c>
-      <c r="I21" s="1">
-        <f>((Feuil1archive!K17-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.14785737651292116</v>
-      </c>
-      <c r="J21" s="1">
-        <f>((Feuil1archive!L17-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.37326407293543939</v>
-      </c>
-      <c r="K21" s="1">
-        <f>((Feuil1archive!M17-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L21" s="1">
-        <f>((Feuil1archive!N17-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M21" s="1">
-        <f>((Feuil1archive!O17-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.13095238095238096</v>
-      </c>
-      <c r="N21" s="1">
-        <f>((Feuil1archive!P17-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.66345202769535117</v>
-      </c>
-      <c r="O21" s="1">
-        <f>((Feuil1archive!Q17-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.47708757637474541</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="1">
-        <f>((Feuil1archive!B18-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.20287187039764362</v>
-      </c>
-      <c r="C22" s="1">
-        <f>((Feuil1archive!C18-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.13025909038866926</v>
-      </c>
-      <c r="D22" s="1">
-        <f>((Feuil1archive!D18-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.21129438130149236</v>
-      </c>
-      <c r="E22" s="1">
-        <f>((Feuil1archive!E18-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.17391581507561343</v>
-      </c>
-      <c r="F22" s="1">
-        <f>((Feuil1archive!G18-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.21318459221685029</v>
-      </c>
-      <c r="G22" s="1">
-        <f>((Feuil1archive!H18-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>4.5943677917876027E-2</v>
-      </c>
-      <c r="H22" s="1">
-        <f>((Feuil1archive!J18-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>8.0536912751677847E-2</v>
-      </c>
-      <c r="I22" s="1">
-        <f>((Feuil1archive!K18-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <f>((Feuil1archive!L18-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>9.0003180324393084E-2</v>
-      </c>
-      <c r="K22" s="1">
-        <f>((Feuil1archive!M18-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L22" s="1">
-        <f>((Feuil1archive!N18-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M22" s="1">
-        <f>((Feuil1archive!O18-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.10367063492063493</v>
-      </c>
-      <c r="N22" s="1">
-        <f>((Feuil1archive!P18-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.21686449060336302</v>
-      </c>
-      <c r="O22" s="1">
-        <f>((Feuil1archive!Q18-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.23421588594704684</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="1">
-        <f>((Feuil1archive!B19-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.20569010345642652</v>
-      </c>
-      <c r="C23" s="1">
-        <f>((Feuil1archive!C19-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.22629831426243088</v>
-      </c>
-      <c r="D23" s="1">
-        <f>((Feuil1archive!D19-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.2096183728831415</v>
-      </c>
-      <c r="E23" s="1">
-        <f>((Feuil1archive!E19-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.14674989702449834</v>
-      </c>
-      <c r="F23" s="1">
-        <f>((Feuil1archive!G19-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.24005310295632876</v>
-      </c>
-      <c r="G23" s="1">
-        <f>((Feuil1archive!H19-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>2.7714699620058156E-3</v>
-      </c>
-      <c r="H23" s="1">
-        <f>((Feuil1archive!J19-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34899328859060402</v>
-      </c>
-      <c r="I23" s="1">
-        <f>((Feuil1archive!K19-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>4.350670592083742E-2</v>
-      </c>
-      <c r="J23" s="1">
-        <f>((Feuil1archive!L19-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.14894519240962578</v>
-      </c>
-      <c r="K23" s="1">
-        <f>((Feuil1archive!M19-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L23" s="1">
-        <f>((Feuil1archive!N19-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M23" s="1">
-        <f>((Feuil1archive!O19-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.10813492063492064</v>
-      </c>
-      <c r="N23" s="1">
-        <f>((Feuil1archive!P19-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.40454995054401582</v>
-      </c>
-      <c r="O23" s="1">
-        <f>((Feuil1archive!Q19-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.29226069246435843</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="1">
-        <f>((Feuil1archive!B20-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.2059741995309006</v>
-      </c>
-      <c r="C24" s="1">
-        <f>((Feuil1archive!C20-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.13025909038866926</v>
-      </c>
-      <c r="D24" s="1">
-        <f>((Feuil1archive!D20-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.21783081413306069</v>
-      </c>
-      <c r="E24" s="1">
-        <f>((Feuil1archive!E20-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.17391581507561343</v>
-      </c>
-      <c r="F24" s="1">
-        <f>((Feuil1archive!G20-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.21859396052944441</v>
-      </c>
-      <c r="G24" s="1">
-        <f>((Feuil1archive!H20-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>3.1071766101429501E-2</v>
-      </c>
-      <c r="H24" s="1">
-        <f>((Feuil1archive!J20-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>8.0536912751677847E-2</v>
-      </c>
-      <c r="I24" s="1">
-        <f>((Feuil1archive!K20-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <f>((Feuil1archive!L20-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>9.0003180324393084E-2</v>
-      </c>
-      <c r="K24" s="1">
-        <f>((Feuil1archive!M20-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L24" s="1">
-        <f>((Feuil1archive!N20-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M24" s="1">
-        <f>((Feuil1archive!O20-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.10367063492063493</v>
-      </c>
-      <c r="N24" s="1">
-        <f>((Feuil1archive!P20-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.21686449060336302</v>
-      </c>
-      <c r="O24" s="1">
-        <f>((Feuil1archive!Q20-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.23421588594704684</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="1">
-        <f>((Feuil1archive!B21-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.20632647866324846</v>
-      </c>
-      <c r="C25" s="1">
-        <f>((Feuil1archive!C21-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.22629831426243088</v>
-      </c>
-      <c r="D25" s="1">
-        <f>((Feuil1archive!D21-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.21095917961782218</v>
-      </c>
-      <c r="E25" s="1">
-        <f>((Feuil1archive!E21-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.14674989702449834</v>
-      </c>
-      <c r="F25" s="1">
-        <f>((Feuil1archive!G21-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.24116271696916858</v>
-      </c>
-      <c r="G25" s="1">
-        <f>((Feuil1archive!H21-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <f>((Feuil1archive!J21-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34899328859060402</v>
-      </c>
-      <c r="I25" s="1">
-        <f>((Feuil1archive!K21-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>4.350670592083742E-2</v>
-      </c>
-      <c r="J25" s="1">
-        <f>((Feuil1archive!L21-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.14894519240962578</v>
-      </c>
-      <c r="K25" s="1">
-        <f>((Feuil1archive!M21-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L25" s="1">
-        <f>((Feuil1archive!N21-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M25" s="1">
-        <f>((Feuil1archive!O21-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.10813492063492064</v>
-      </c>
-      <c r="N25" s="1">
-        <f>((Feuil1archive!P21-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.40454995054401582</v>
-      </c>
-      <c r="O25" s="1">
-        <f>((Feuil1archive!Q21-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.29226069246435843</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="1">
-        <f>((Feuil1archive!B22-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.2059741995309006</v>
-      </c>
-      <c r="C26" s="1">
-        <f>((Feuil1archive!C22-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.13025909038866926</v>
-      </c>
-      <c r="D26" s="1">
-        <f>((Feuil1archive!D22-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.21783081413306069</v>
-      </c>
-      <c r="E26" s="1">
-        <f>((Feuil1archive!E22-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.17391581507561343</v>
-      </c>
-      <c r="F26" s="1">
-        <f>((Feuil1archive!G22-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.21859396052944441</v>
-      </c>
-      <c r="G26" s="1">
-        <f>((Feuil1archive!H22-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>3.1071766101429501E-2</v>
-      </c>
-      <c r="H26" s="1">
-        <f>((Feuil1archive!J22-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>8.0536912751677847E-2</v>
-      </c>
-      <c r="I26" s="1">
-        <f>((Feuil1archive!K22-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <f>((Feuil1archive!L22-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>9.0003180324393084E-2</v>
-      </c>
-      <c r="K26" s="1">
-        <f>((Feuil1archive!M22-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L26" s="1">
-        <f>((Feuil1archive!N22-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M26" s="1">
-        <f>((Feuil1archive!O22-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.10367063492063493</v>
-      </c>
-      <c r="N26" s="1">
-        <f>((Feuil1archive!P22-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.21686449060336302</v>
-      </c>
-      <c r="O26" s="1">
-        <f>((Feuil1archive!Q22-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.23421588594704684</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="1">
-        <f>((Feuil1archive!B23-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.48272923144057167</v>
-      </c>
-      <c r="C27" s="1">
-        <f>((Feuil1archive!C23-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.29095305123214421</v>
-      </c>
-      <c r="D27" s="1">
-        <f>((Feuil1archive!D23-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.33397819752477498</v>
-      </c>
-      <c r="E27" s="1">
-        <f>((Feuil1archive!E23-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.59359002020281271</v>
-      </c>
-      <c r="F27" s="1">
-        <f>((Feuil1archive!G23-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.36199175715304749</v>
-      </c>
-      <c r="G27" s="1">
-        <f>((Feuil1archive!H23-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.59676622354422082</v>
-      </c>
-      <c r="H27" s="1">
-        <f>((Feuil1archive!J23-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.34899328859060402</v>
-      </c>
-      <c r="I27" s="1">
-        <f>((Feuil1archive!K23-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>9.2574419365390903E-2</v>
-      </c>
-      <c r="J27" s="1">
-        <f>((Feuil1archive!L23-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.29078766034135484</v>
-      </c>
-      <c r="K27" s="1">
-        <f>((Feuil1archive!M23-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.12544353997077856</v>
-      </c>
-      <c r="L27" s="1">
-        <f>((Feuil1archive!N23-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M27" s="1">
-        <f>((Feuil1archive!O23-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.14136904761904762</v>
-      </c>
-      <c r="N27" s="1">
-        <f>((Feuil1archive!P23-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.33234421364985162</v>
-      </c>
-      <c r="O27" s="1">
-        <f>((Feuil1archive!Q23-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.40224032586558045</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="1">
-        <f>((Feuil1archive!B25-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.16524618629429627</v>
-      </c>
-      <c r="C28" s="1">
-        <f>((Feuil1archive!C25-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.36759585401499184</v>
-      </c>
-      <c r="D28" s="1">
-        <f>((Feuil1archive!D25-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.1328332443452673</v>
-      </c>
-      <c r="E28" s="1">
-        <f>((Feuil1archive!E25-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>8.6680854402447868E-2</v>
-      </c>
-      <c r="F28" s="1">
-        <f>((Feuil1archive!G25-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.21807878259491162</v>
-      </c>
-      <c r="G28" s="1">
-        <f>((Feuil1archive!H25-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>5.8574915804237092E-2</v>
-      </c>
-      <c r="H28" s="1">
-        <f>((Feuil1archive!J25-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="I28" s="1">
-        <f>((Feuil1archive!K25-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.11432777232580962</v>
-      </c>
-      <c r="J28" s="1">
-        <f>((Feuil1archive!L25-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.10548075903742182</v>
-      </c>
-      <c r="K28" s="1">
-        <f>((Feuil1archive!M25-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.35086620747234398</v>
-      </c>
-      <c r="L28" s="1">
-        <f>((Feuil1archive!N25-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>4.9370764762826716E-2</v>
-      </c>
-      <c r="M28" s="1">
-        <f>((Feuil1archive!O25-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.39632936507936506</v>
-      </c>
-      <c r="N28" s="1">
-        <f>((Feuil1archive!P25-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.57467853610286845</v>
-      </c>
-      <c r="O28" s="1">
-        <f>((Feuil1archive!Q25-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.42769857433808556</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O29" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="1">
-        <f>((Feuil1archive!B26-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.45411507481954222</v>
-      </c>
-      <c r="C30" s="1">
-        <f>((Feuil1archive!C26-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.62466578215394564</v>
-      </c>
-      <c r="D30" s="1">
-        <f>((Feuil1archive!D26-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.2237447295520987</v>
-      </c>
-      <c r="E30" s="1">
-        <f>((Feuil1archive!E26-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.52324794539356256</v>
-      </c>
-      <c r="F30" s="1">
-        <f>((Feuil1archive!G26-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.36894665926923992</v>
-      </c>
-      <c r="G30" s="1">
-        <f>((Feuil1archive!H26-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.56416299492883204</v>
-      </c>
-      <c r="H30" s="1">
-        <f>((Feuil1archive!J26-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.51006711409395977</v>
-      </c>
-      <c r="I30" s="1">
-        <f>((Feuil1archive!K26-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.24223094537127904</v>
-      </c>
-      <c r="J30" s="1">
-        <f>((Feuil1archive!L26-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.42118096045796671</v>
-      </c>
-      <c r="K30" s="1">
-        <f>((Feuil1archive!M26-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.23815487372156127</v>
-      </c>
-      <c r="L30" s="1">
-        <f>((Feuil1archive!N26-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.26815101645692158</v>
-      </c>
-      <c r="M30" s="1">
-        <f>((Feuil1archive!O26-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.5982142857142857</v>
-      </c>
-      <c r="N30" s="1">
-        <f>((Feuil1archive!P26-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.70771513353115723</v>
-      </c>
-      <c r="O30" s="1">
-        <f>((Feuil1archive!Q26-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.70112016293279023</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="1">
-        <f>((Feuil1archive!B27-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.45412643866252117</v>
-      </c>
-      <c r="C31" s="1">
-        <f>((Feuil1archive!C27-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.63598036112364542</v>
-      </c>
-      <c r="D31" s="1">
-        <f>((Feuil1archive!D27-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.21974625232546166</v>
-      </c>
-      <c r="E31" s="1">
-        <f>((Feuil1archive!E27-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.52324794539356256</v>
-      </c>
-      <c r="F31" s="1">
-        <f>((Feuil1archive!G27-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.36896647380518349</v>
-      </c>
-      <c r="G31" s="1">
-        <f>((Feuil1archive!H27-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.56411412924105453</v>
-      </c>
-      <c r="H31" s="1">
-        <f>((Feuil1archive!J27-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.51006711409395977</v>
-      </c>
-      <c r="I31" s="1">
-        <f>((Feuil1archive!K27-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.28655544651619236</v>
-      </c>
-      <c r="J31" s="1">
-        <f>((Feuil1archive!L27-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.42118096045796671</v>
-      </c>
-      <c r="K31" s="1">
-        <f>((Feuil1archive!M27-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.23815487372156127</v>
-      </c>
-      <c r="L31" s="1">
-        <f>((Feuil1archive!N27-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.26815101645692158</v>
-      </c>
-      <c r="M31" s="1">
-        <f>((Feuil1archive!O27-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.59077380952380953</v>
-      </c>
-      <c r="N31" s="1">
-        <f>((Feuil1archive!P27-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.6708704253214639</v>
-      </c>
-      <c r="O31" s="1">
-        <f>((Feuil1archive!Q27-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.73217922606924646</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="1">
-        <f>((Feuil1archive!B28-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.45410371097656327</v>
-      </c>
-      <c r="C32" s="1">
-        <f>((Feuil1archive!C28-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.61725742687616603</v>
-      </c>
-      <c r="D32" s="1">
-        <f>((Feuil1archive!D28-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.22635451408924503</v>
-      </c>
-      <c r="E32" s="1">
-        <f>((Feuil1archive!E28-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.52324794539356256</v>
-      </c>
-      <c r="F32" s="1">
-        <f>((Feuil1archive!G28-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.36892684473329634</v>
-      </c>
-      <c r="G32" s="1">
-        <f>((Feuil1archive!H28-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.56421186411052715</v>
-      </c>
-      <c r="H32" s="1">
-        <f>((Feuil1archive!J28-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.51006711409395977</v>
-      </c>
-      <c r="I32" s="1">
-        <f>((Feuil1archive!K28-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.30062152437029765</v>
-      </c>
-      <c r="J32" s="1">
-        <f>((Feuil1archive!L28-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.42118096045796671</v>
-      </c>
-      <c r="K32" s="1">
-        <f>((Feuil1archive!M28-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.23815487372156127</v>
-      </c>
-      <c r="L32" s="1">
-        <f>((Feuil1archive!N28-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.31461761858664083</v>
-      </c>
-      <c r="M32" s="1">
-        <f>((Feuil1archive!O28-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.59077380952380953</v>
-      </c>
-      <c r="N32" s="1">
-        <f>((Feuil1archive!P28-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.58382789317507422</v>
-      </c>
-      <c r="O32" s="1">
-        <f>((Feuil1archive!Q28-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.70162932790224031</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="1">
-        <f>((Feuil1archive!B29-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.55233276968672163</v>
-      </c>
-      <c r="C33" s="1">
-        <f>((Feuil1archive!C29-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.47818239370693894</v>
-      </c>
-      <c r="D33" s="1">
-        <f>((Feuil1archive!D29-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.44289480174017559</v>
-      </c>
-      <c r="E33" s="1">
-        <f>((Feuil1archive!E29-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.56407037639997648</v>
-      </c>
-      <c r="F33" s="1">
-        <f>((Feuil1archive!G29-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.50721249108345878</v>
-      </c>
-      <c r="G33" s="1">
-        <f>((Feuil1archive!H29-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.546604717525907</v>
-      </c>
-      <c r="H33" s="1">
-        <f>((Feuil1archive!J29-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I33" s="1">
-        <f>((Feuil1archive!K29-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.10827608766764803</v>
-      </c>
-      <c r="J33" s="1">
-        <f>((Feuil1archive!L29-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.44725962048128909</v>
-      </c>
-      <c r="K33" s="1">
-        <f>((Feuil1archive!M29-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.23815487372156127</v>
-      </c>
-      <c r="L33" s="1">
-        <f>((Feuil1archive!N29-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>3.8722168441432718E-2</v>
-      </c>
-      <c r="M33" s="1">
-        <f>((Feuil1archive!O29-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.18253968253968253</v>
-      </c>
-      <c r="N33" s="1">
-        <f>((Feuil1archive!P29-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.54277942631058362</v>
-      </c>
-      <c r="O33" s="1">
-        <f>((Feuil1archive!Q29-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.83503054989816705</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="1">
-        <f>((Feuil1archive!B30-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.51061610211094755</v>
-      </c>
-      <c r="C34" s="1">
-        <f>((Feuil1archive!C30-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.95359675648736197</v>
-      </c>
-      <c r="D34" s="1">
-        <f>((Feuil1archive!D30-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.14595399596321398</v>
-      </c>
-      <c r="E34" s="1">
-        <f>((Feuil1archive!E30-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.6050644332424534</v>
-      </c>
-      <c r="F34" s="1">
-        <f>((Feuil1archive!G30-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.40134342553697394</v>
-      </c>
-      <c r="G34" s="1">
-        <f>((Feuil1archive!H30-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.85570243058607431</v>
-      </c>
-      <c r="H34" s="1">
-        <f>((Feuil1archive!J30-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I34" s="1">
-        <f>((Feuil1archive!K30-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.66961072947333988</v>
-      </c>
-      <c r="J34" s="1">
-        <f>((Feuil1archive!L30-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.60606381850948798</v>
-      </c>
-      <c r="K34" s="1">
-        <f>((Feuil1archive!M30-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.56237389549850414</v>
-      </c>
-      <c r="L34" s="1">
-        <f>((Feuil1archive!N30-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.39883833494675702</v>
-      </c>
-      <c r="M34" s="1">
-        <f>((Feuil1archive!O30-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.16617063492063491</v>
-      </c>
-      <c r="N34" s="1">
-        <f>((Feuil1archive!P30-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="O34" s="1">
-        <f>((Feuil1archive!Q30-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.94908350305498979</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="1">
-        <f>((Feuil1archive!B31-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.51061610211094755</v>
-      </c>
-      <c r="C35" s="1">
-        <f>((Feuil1archive!C31-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.93931883540655037</v>
-      </c>
-      <c r="D35" s="1">
-        <f>((Feuil1archive!D31-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.1510299071730766</v>
-      </c>
-      <c r="E35" s="1">
-        <f>((Feuil1archive!E31-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.6050644332424534</v>
-      </c>
-      <c r="F35" s="1">
-        <f>((Feuil1archive!G31-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.40134342553697394</v>
-      </c>
-      <c r="G35" s="1">
-        <f>((Feuil1archive!H31-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.85570243058607431</v>
-      </c>
-      <c r="H35" s="1">
-        <f>((Feuil1archive!J31-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I35" s="1">
-        <f>((Feuil1archive!K31-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.65080143931959433</v>
-      </c>
-      <c r="J35" s="1">
-        <f>((Feuil1archive!L31-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.62111735397010492</v>
-      </c>
-      <c r="K35" s="1">
-        <f>((Feuil1archive!M31-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.56237389549850414</v>
-      </c>
-      <c r="L35" s="1">
-        <f>((Feuil1archive!N31-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.39883833494675702</v>
-      </c>
-      <c r="M35" s="1">
-        <f>((Feuil1archive!O31-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.16617063492063491</v>
-      </c>
-      <c r="N35" s="1">
-        <f>((Feuil1archive!P31-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="O35" s="1">
-        <f>((Feuil1archive!Q31-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.86354378818737276</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="1">
-        <f>((Feuil1archive!B32-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.51099110892925326</v>
-      </c>
-      <c r="C36" s="1">
-        <f>((Feuil1archive!C32-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="1">
-        <f>((Feuil1archive!D32-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.13024740278552599</v>
-      </c>
-      <c r="E36" s="1">
-        <f>((Feuil1archive!E32-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.6050644332424534</v>
-      </c>
-      <c r="F36" s="1">
-        <f>((Feuil1archive!G32-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.40199730522311167</v>
-      </c>
-      <c r="G36" s="1">
-        <f>((Feuil1archive!H32-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.85393060167969459</v>
-      </c>
-      <c r="H36" s="1">
-        <f>((Feuil1archive!J32-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I36" s="1">
-        <f>((Feuil1archive!K32-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="J36" s="1">
-        <f>((Feuil1archive!L32-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.55899501749178415</v>
-      </c>
-      <c r="K36" s="1">
-        <f>((Feuil1archive!M32-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.56237389549850414</v>
-      </c>
-      <c r="L36" s="1">
-        <f>((Feuil1archive!N32-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.39883833494675702</v>
-      </c>
-      <c r="M36" s="1">
-        <f>((Feuil1archive!O32-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.16617063492063491</v>
-      </c>
-      <c r="N36" s="1">
-        <f>((Feuil1archive!P32-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.70103857566765582</v>
-      </c>
-      <c r="O36" s="1">
-        <f>((Feuil1archive!Q32-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="1">
-        <f>((Feuil1archive!B33-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.51060473826796859</v>
-      </c>
-      <c r="C37" s="1">
-        <f>((Feuil1archive!C33-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.6632565782827432</v>
-      </c>
-      <c r="D37" s="1">
-        <f>((Feuil1archive!D33-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.24914822857881666</v>
-      </c>
-      <c r="E37" s="1">
-        <f>((Feuil1archive!E33-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.6050644332424534</v>
-      </c>
-      <c r="F37" s="1">
-        <f>((Feuil1archive!G33-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.40132361100103037</v>
-      </c>
-      <c r="G37" s="1">
-        <f>((Feuil1archive!H33-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.85575618225876859</v>
-      </c>
-      <c r="H37" s="1">
-        <f>((Feuil1archive!J33-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I37" s="1">
-        <f>((Feuil1archive!K33-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.22980045796532547</v>
-      </c>
-      <c r="J37" s="1">
-        <f>((Feuil1archive!L33-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.49305629174175764</v>
-      </c>
-      <c r="K37" s="1">
-        <f>((Feuil1archive!M33-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.56237389549850414</v>
-      </c>
-      <c r="L37" s="1">
-        <f>((Feuil1archive!N33-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.39883833494675702</v>
-      </c>
-      <c r="M37" s="1">
-        <f>((Feuil1archive!O33-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.16617063492063491</v>
-      </c>
-      <c r="N37" s="1">
-        <f>((Feuil1archive!P33-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.87512363996043518</v>
-      </c>
-      <c r="O37" s="1">
-        <f>((Feuil1archive!Q33-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.65173116089613037</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="1">
-        <f>((Feuil1archive!B34-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.51061610211094755</v>
-      </c>
-      <c r="C38" s="1">
-        <f>((Feuil1archive!C34-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.62325145978273311</v>
-      </c>
-      <c r="D38" s="1">
-        <f>((Feuil1archive!D34-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.26339430013479892</v>
-      </c>
-      <c r="E38" s="1">
-        <f>((Feuil1archive!E34-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.6050644332424534</v>
-      </c>
-      <c r="F38" s="1">
-        <f>((Feuil1archive!G34-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.40134342553697394</v>
-      </c>
-      <c r="G38" s="1">
-        <f>((Feuil1archive!H34-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>0.85570243058607431</v>
-      </c>
-      <c r="H38" s="1">
-        <f>((Feuil1archive!J34-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I38" s="1">
-        <f>((Feuil1archive!K34-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.19414458619561661</v>
-      </c>
-      <c r="J38" s="1">
-        <f>((Feuil1archive!L34-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.49793278914449274</v>
-      </c>
-      <c r="K38" s="1">
-        <f>((Feuil1archive!M34-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>0.56237389549850414</v>
-      </c>
-      <c r="L38" s="1">
-        <f>((Feuil1archive!N34-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.39883833494675702</v>
-      </c>
-      <c r="M38" s="1">
-        <f>((Feuil1archive!O34-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.16617063492063491</v>
-      </c>
-      <c r="N38" s="1">
-        <f>((Feuil1archive!P34-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.79698318496538079</v>
-      </c>
-      <c r="O38" s="1">
-        <f>((Feuil1archive!Q34-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0.60947046843177188</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O39" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="1">
-        <f>((Feuil1archive!B35-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>0.44676266841215301</v>
-      </c>
-      <c r="C40" s="1">
-        <f>((Feuil1archive!C35-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>0.69464106518679158</v>
-      </c>
-      <c r="D40" s="1">
-        <f>((Feuil1archive!D35-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>0.14803703499745005</v>
-      </c>
-      <c r="E40" s="1">
-        <f>((Feuil1archive!E35-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>0.55943647882627545</v>
-      </c>
-      <c r="F40" s="1">
-        <f>((Feuil1archive!G35-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>0.32688039946104464</v>
-      </c>
-      <c r="G40" s="1">
-        <f>((Feuil1archive!H35-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="H40" s="1">
-        <f>((Feuil1archive!J35-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>0.93288590604026844</v>
-      </c>
-      <c r="I40" s="1">
-        <f>((Feuil1archive!K35-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>0.73405299313052008</v>
-      </c>
-      <c r="J40" s="1">
-        <f>((Feuil1archive!L35-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>0.44513940421923037</v>
-      </c>
-      <c r="K40" s="1">
-        <f>((Feuil1archive!M35-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>1</v>
-      </c>
-      <c r="L40" s="1">
-        <f>((Feuil1archive!N35-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>0.22652468538238141</v>
-      </c>
-      <c r="M40" s="1">
-        <f>((Feuil1archive!O35-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>0.51537698412698407</v>
-      </c>
-      <c r="N40" s="1">
-        <f>((Feuil1archive!P35-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>0.31478733926805141</v>
-      </c>
-      <c r="O40" s="1">
-        <f>((Feuil1archive!Q35-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!B$2:B$35))/(MAX(Feuil1archive!B$2:B$35) - MIN(Feuil1archive!B$2:B$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!C$2:C$35))/(MAX(Feuil1archive!C$2:C$35) - MIN(Feuil1archive!C$2:C$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!D$2:D$35))/(MAX(Feuil1archive!D$2:D$35) - MIN(Feuil1archive!D$2:D$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!E$2:E$35))/(MAX(Feuil1archive!E$2:E$35) - MIN(Feuil1archive!E$2:E$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!G$2:G$35))/(MAX(Feuil1archive!G$2:G$35) - MIN(Feuil1archive!G$2:G$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!H$2:H$35))/(MAX(Feuil1archive!H$2:H$35) - MIN(Feuil1archive!H$2:H$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!J$2:J$35))/(MAX(Feuil1archive!J$2:J$35) - MIN(Feuil1archive!J$2:J$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!K$2:K$35))/(MAX(Feuil1archive!K$2:K$35) - MIN(Feuil1archive!K$2:K$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!L$2:L$35))/(MAX(Feuil1archive!L$2:L$35) - MIN(Feuil1archive!L$2:L$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!M$2:M$35))/(MAX(Feuil1archive!M$2:M$35) - MIN(Feuil1archive!M$2:M$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!N$2:N$35))/(MAX(Feuil1archive!N$2:N$35) - MIN(Feuil1archive!N$2:N$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!O$2:O$35))/(MAX(Feuil1archive!O$2:O$35) - MIN(Feuil1archive!O$2:O$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!P$2:P$35))/(MAX(Feuil1archive!P$2:P$35) - MIN(Feuil1archive!P$2:P$35)))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O41" s="1" t="e">
-        <f>((Feuil1archive!#REF!-MIN(Feuil1archive!Q$2:Q$35))/(MAX(Feuil1archive!Q$2:Q$35) - MIN(Feuil1archive!Q$2:Q$35)))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/subsystems database (normalised).xlsx
+++ b/subsystems database (normalised).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A1882C-CE30-4204-814E-ABC4595AE6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B49B26-61D7-47BA-AE87-B07F66CB47AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15132" windowHeight="12336" activeTab="2" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
     <sheet name="outliers removed" sheetId="4" r:id="rId1"/>
@@ -20,15 +20,16 @@
     <sheet name="H2 fuel cells" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Feuil1archive!$B$2:$B$35</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Feuil1archive!$L$2:$L$35</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Feuil1archive!$K$2:$K$35</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Feuil1archive!$L$2:$L$35</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Feuil1archive!$M$2:$M$35</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Feuil1archive!$M$2:$M$35</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Feuil1archive!$AB$2:$AB$35</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">Feuil1archive!$N$2:$N$35</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">Feuil1archive!$O$2:$O$35</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Feuil1archive!$AB$2:$AB$35</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Feuil1archive!$B$2:$B$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -611,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -681,15 +682,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -9311,7 +9303,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -9451,7 +9443,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -9521,7 +9513,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -9731,7 +9723,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -21884,8 +21876,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11979728" y="10146871"/>
-              <a:ext cx="5157652" cy="3124794"/>
+              <a:off x="11655878" y="10569781"/>
+              <a:ext cx="5153842" cy="3254334"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -21962,8 +21954,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11925300" y="13548360"/>
-              <a:ext cx="5212080" cy="3124795"/>
+              <a:off x="11601450" y="14116050"/>
+              <a:ext cx="5208270" cy="3254335"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22040,8 +22032,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11925300" y="16988642"/>
-              <a:ext cx="5181600" cy="3124794"/>
+              <a:off x="11601450" y="17693492"/>
+              <a:ext cx="5177790" cy="3254334"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22118,8 +22110,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11925300" y="20314920"/>
-              <a:ext cx="5013960" cy="3124794"/>
+              <a:off x="11601450" y="21164550"/>
+              <a:ext cx="4895850" cy="3254334"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22196,8 +22188,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11925300" y="23789640"/>
-              <a:ext cx="5151120" cy="3124794"/>
+              <a:off x="11601450" y="24784050"/>
+              <a:ext cx="5147310" cy="3254334"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22274,8 +22266,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11925300" y="27081480"/>
-              <a:ext cx="5143500" cy="3124794"/>
+              <a:off x="11601450" y="28213050"/>
+              <a:ext cx="5139690" cy="3254334"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22352,8 +22344,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="17846040" y="13548360"/>
-              <a:ext cx="5475119" cy="3124795"/>
+              <a:off x="19859625" y="14116050"/>
+              <a:ext cx="5299859" cy="3254335"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22818,12 +22810,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79267561-2A2B-42DC-9CFC-64E98D3091CC}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -22879,7 +22871,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>12</v>
       </c>
@@ -22942,7 +22934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
@@ -23007,7 +22999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
@@ -23068,7 +23060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
@@ -23129,7 +23121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -23192,7 +23184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>17</v>
       </c>
@@ -23256,7 +23248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>18</v>
       </c>
@@ -23320,7 +23312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
@@ -23384,7 +23376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>20</v>
       </c>
@@ -23448,7 +23440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>30</v>
       </c>
@@ -23514,7 +23506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>31</v>
       </c>
@@ -23580,7 +23572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>34</v>
       </c>
@@ -23647,7 +23639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>35</v>
       </c>
@@ -23714,7 +23706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>36</v>
       </c>
@@ -23781,7 +23773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>37</v>
       </c>
@@ -23847,7 +23839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>38</v>
       </c>
@@ -23912,7 +23904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>39</v>
       </c>
@@ -23977,7 +23969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>41</v>
       </c>
@@ -24043,7 +24035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>42</v>
       </c>
@@ -24108,7 +24100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>60</v>
       </c>
@@ -24175,7 +24167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>44</v>
       </c>
@@ -24243,7 +24235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>45</v>
       </c>
@@ -24310,7 +24302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>46</v>
       </c>
@@ -24376,7 +24368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>47</v>
       </c>
@@ -24443,7 +24435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>49</v>
       </c>
@@ -24508,7 +24500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>53</v>
       </c>
@@ -24575,7 +24567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>54</v>
       </c>
@@ -24663,13 +24655,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FB372F-B6E8-4845-B0EA-74D8461302A1}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>21</v>
       </c>
@@ -24716,7 +24708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>12</v>
       </c>
@@ -24777,7 +24769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>13</v>
       </c>
@@ -24838,7 +24830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>14</v>
       </c>
@@ -24899,7 +24891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>15</v>
       </c>
@@ -24960,7 +24952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>22</v>
       </c>
@@ -25021,7 +25013,7 @@
         <v>0.95621181262729127</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>16</v>
       </c>
@@ -25082,7 +25074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>17</v>
       </c>
@@ -25143,7 +25135,7 @@
         <v>0.76782077393075354</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>18</v>
       </c>
@@ -25204,7 +25196,7 @@
         <v>0.75509164969450104</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>19</v>
       </c>
@@ -25265,7 +25257,7 @@
         <v>0.60794297352342164</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>20</v>
       </c>
@@ -25326,7 +25318,7 @@
         <v>0.60183299389002032</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>23</v>
       </c>
@@ -25387,7 +25379,7 @@
         <v>0.68024439918533608</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>28</v>
       </c>
@@ -25448,7 +25440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>30</v>
       </c>
@@ -25509,7 +25501,7 @@
         <v>0.52087576374745415</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>31</v>
       </c>
@@ -25570,7 +25562,7 @@
         <v>0.78309572301425667</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>34</v>
       </c>
@@ -25631,7 +25623,7 @@
         <v>0.40071283095723015</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>35</v>
       </c>
@@ -25692,7 +25684,7 @@
         <v>0.47708757637474541</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>36</v>
       </c>
@@ -25753,7 +25745,7 @@
         <v>0.23421588594704684</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>37</v>
       </c>
@@ -25814,7 +25806,7 @@
         <v>0.29226069246435843</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>38</v>
       </c>
@@ -25875,7 +25867,7 @@
         <v>0.23421588594704684</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>39</v>
       </c>
@@ -25936,7 +25928,7 @@
         <v>0.29226069246435843</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
@@ -25997,7 +25989,7 @@
         <v>0.23421588594704684</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>42</v>
       </c>
@@ -26058,7 +26050,7 @@
         <v>0.40224032586558045</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>44</v>
       </c>
@@ -26119,7 +26111,7 @@
         <v>0.42769857433808556</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>45</v>
       </c>
@@ -26180,7 +26172,7 @@
         <v>0.70112016293279023</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>46</v>
       </c>
@@ -26241,7 +26233,7 @@
         <v>0.73217922606924646</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>47</v>
       </c>
@@ -26302,7 +26294,7 @@
         <v>0.70162932790224031</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>49</v>
       </c>
@@ -26363,7 +26355,7 @@
         <v>0.83503054989816705</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>50</v>
       </c>
@@ -26424,7 +26416,7 @@
         <v>0.94908350305498979</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>51</v>
       </c>
@@ -26485,7 +26477,7 @@
         <v>0.86354378818737276</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>52</v>
       </c>
@@ -26546,7 +26538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>53</v>
       </c>
@@ -26607,7 +26599,7 @@
         <v>0.65173116089613037</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>54</v>
       </c>
@@ -26668,7 +26660,7 @@
         <v>0.60947046843177188</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
         <v>55</v>
       </c>
@@ -26737,29 +26729,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
   <dimension ref="A1:AB57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" customWidth="1"/>
-    <col min="7" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="7.77734375" customWidth="1"/>
-    <col min="10" max="14" width="11.5546875" customWidth="1"/>
-    <col min="15" max="15" width="17.88671875" customWidth="1"/>
-    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.6640625" customWidth="1"/>
-    <col min="19" max="20" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.6640625" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.109375" customWidth="1"/>
-    <col min="24" max="24" width="11.5546875" style="19"/>
+    <col min="3" max="3" width="7.28515625" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="14" width="11.5703125" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" customWidth="1"/>
+    <col min="19" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.140625" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="19"/>
     <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -26833,7 +26825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>12</v>
       </c>
@@ -26916,7 +26908,7 @@
         <v>5.9997391417764445E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
@@ -27000,7 +26992,7 @@
         <v>0.30113500597371567</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
@@ -27081,7 +27073,7 @@
         <v>4.8272693334864891E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
@@ -27162,7 +27154,7 @@
         <v>5.9424298610900025E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -27244,7 +27236,7 @@
         <v>3.6206684940473757E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
@@ -27324,7 +27316,7 @@
         <v>0.12643935660199829</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>17</v>
       </c>
@@ -27408,7 +27400,7 @@
         <v>5.6842224040170385E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>18</v>
       </c>
@@ -27492,7 +27484,7 @@
         <v>5.9868500422246354E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>19</v>
       </c>
@@ -27576,7 +27568,7 @@
         <v>7.0418308009754266E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>20</v>
       </c>
@@ -27660,7 +27652,7 @@
         <v>7.2966929504531014E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -27745,7 +27737,7 @@
         <v>1.8051759624793332E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>28</v>
       </c>
@@ -27807,7 +27799,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S13" s="25" t="s">
+      <c r="S13" s="24" t="s">
         <v>65</v>
       </c>
       <c r="T13" s="24" t="s">
@@ -27828,7 +27820,7 @@
         <v>0.15017787904225127</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>30</v>
       </c>
@@ -27893,7 +27885,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S14" s="26" t="s">
+      <c r="S14" s="23" t="s">
         <v>65</v>
       </c>
       <c r="T14" s="23" t="s">
@@ -27916,7 +27908,7 @@
         <v>5.3620465385171269E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>31</v>
       </c>
@@ -27981,7 +27973,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S15" s="27">
+      <c r="S15" s="1">
         <v>4.5</v>
       </c>
       <c r="T15" s="1">
@@ -28002,7 +27994,7 @@
         <v>4.6641862605960649E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>34</v>
       </c>
@@ -28092,7 +28084,7 @@
         <v>6.8232435715731926E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>35</v>
       </c>
@@ -28182,7 +28174,7 @@
         <v>7.9304693901439779E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>36</v>
       </c>
@@ -28269,7 +28261,7 @@
         <v>3.6274430949891419E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>37</v>
       </c>
@@ -28355,7 +28347,7 @@
         <v>5.199796939589528E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>38</v>
       </c>
@@ -28440,7 +28432,7 @@
         <v>3.5495041712576739E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>39</v>
       </c>
@@ -28525,7 +28517,7 @@
         <v>5.1787648970747564E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>41</v>
       </c>
@@ -28611,7 +28603,7 @@
         <v>3.5495041712576739E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>42</v>
       </c>
@@ -28699,7 +28691,7 @@
         <v>5.0995336709622426E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>60</v>
       </c>
@@ -28769,7 +28761,7 @@
         <v>4.5</v>
       </c>
       <c r="T24" s="1">
-        <f t="shared" ref="T24:T25" si="10">S24*V24*24</f>
+        <f t="shared" ref="T24" si="10">S24*V24*24</f>
         <v>756</v>
       </c>
       <c r="U24" s="23" t="s">
@@ -28789,7 +28781,7 @@
         <v>5.155632160600223E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>44</v>
       </c>
@@ -28877,7 +28869,7 @@
         <v>9.069400630914827E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>45</v>
       </c>
@@ -28963,7 +28955,7 @@
         <v>9.5200551887257318E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>46</v>
       </c>
@@ -29048,7 +29040,7 @@
         <v>0.10854890367085489</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>47</v>
       </c>
@@ -29137,7 +29129,7 @@
         <v>0.11279751638496033</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>49</v>
       </c>
@@ -29221,7 +29213,7 @@
         <v>4.0811088295687886E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>50</v>
       </c>
@@ -29307,7 +29299,7 @@
         <v>0.20725979296821562</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>51</v>
       </c>
@@ -29393,7 +29385,7 @@
         <v>0.20201559578640157</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>52</v>
       </c>
@@ -29480,7 +29472,7 @@
         <v>0.29892541662872235</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>53</v>
       </c>
@@ -29566,7 +29558,7 @@
         <v>8.4640642101422844E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>54</v>
       </c>
@@ -29651,7 +29643,7 @@
         <v>7.4695608554881665E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>55</v>
       </c>
@@ -29737,7 +29729,7 @@
         <v>0.27180672500137582</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -29758,7 +29750,7 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -29779,7 +29771,7 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -29800,7 +29792,7 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -29821,7 +29813,7 @@
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
     </row>
-    <row r="57" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O57" s="19"/>
     </row>
   </sheetData>
@@ -29846,13 +29838,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B907E4B-21C2-4309-910A-73EEB4277112}">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -29899,7 +29891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>12</v>
       </c>
@@ -29957,7 +29949,7 @@
       </c>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
@@ -30015,7 +30007,7 @@
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
@@ -30073,7 +30065,7 @@
       </c>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
@@ -30131,7 +30123,7 @@
       </c>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -30189,7 +30181,7 @@
       </c>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
@@ -30247,7 +30239,7 @@
       </c>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>17</v>
       </c>
@@ -30305,7 +30297,7 @@
       </c>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>18</v>
       </c>
@@ -30363,7 +30355,7 @@
       </c>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>19</v>
       </c>
@@ -30421,7 +30413,7 @@
       </c>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>20</v>
       </c>
@@ -30479,7 +30471,7 @@
       </c>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
@@ -30537,7 +30529,7 @@
       </c>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>28</v>
       </c>
@@ -30595,7 +30587,7 @@
       </c>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>30</v>
       </c>
@@ -30653,7 +30645,7 @@
       </c>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>31</v>
       </c>
@@ -30711,7 +30703,7 @@
       </c>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>34</v>
       </c>
@@ -30769,7 +30761,7 @@
       </c>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>35</v>
       </c>
@@ -30827,7 +30819,7 @@
       </c>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>36</v>
       </c>
@@ -30885,7 +30877,7 @@
       </c>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>37</v>
       </c>
@@ -30943,7 +30935,7 @@
       </c>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>38</v>
       </c>
@@ -31001,7 +30993,7 @@
       </c>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>39</v>
       </c>
@@ -31059,7 +31051,7 @@
       </c>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>41</v>
       </c>
@@ -31117,7 +31109,7 @@
       </c>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>42</v>
       </c>
@@ -31175,7 +31167,7 @@
       </c>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>60</v>
       </c>
@@ -31233,7 +31225,7 @@
       </c>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>44</v>
       </c>
@@ -31291,7 +31283,7 @@
       </c>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>45</v>
       </c>
@@ -31349,7 +31341,7 @@
       </c>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>46</v>
       </c>
@@ -31407,7 +31399,7 @@
       </c>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>47</v>
       </c>
@@ -31465,7 +31457,7 @@
       </c>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>49</v>
       </c>
@@ -31523,7 +31515,7 @@
       </c>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>50</v>
       </c>
@@ -31581,7 +31573,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>51</v>
       </c>
@@ -31639,7 +31631,7 @@
       </c>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>52</v>
       </c>
@@ -31697,7 +31689,7 @@
       </c>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>53</v>
       </c>
@@ -31755,7 +31747,7 @@
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>54</v>
       </c>
@@ -31813,7 +31805,7 @@
       </c>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>55</v>
       </c>
@@ -31880,17 +31872,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4F88C4-C3FC-484A-AF2F-6A7A136EE5CD}">
   <dimension ref="B2:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>68</v>
       </c>
@@ -31913,7 +31905,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>71</v>
       </c>
@@ -31929,7 +31921,7 @@
       <c r="F3" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="25">
         <f>D3/C3</f>
         <v>101.69491525423729</v>
       </c>
